--- a/data/nzd0510/nzd0510.xlsx
+++ b/data/nzd0510/nzd0510.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R458"/>
+  <dimension ref="A1:R459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27822,6 +27822,66 @@
       <c r="R458" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>264.23</v>
+      </c>
+      <c r="C459" t="n">
+        <v>310.63</v>
+      </c>
+      <c r="D459" t="n">
+        <v>319.54</v>
+      </c>
+      <c r="E459" t="n">
+        <v>325.06</v>
+      </c>
+      <c r="F459" t="n">
+        <v>325.7</v>
+      </c>
+      <c r="G459" t="n">
+        <v>322.95</v>
+      </c>
+      <c r="H459" t="n">
+        <v>283.21</v>
+      </c>
+      <c r="I459" t="n">
+        <v>281.57</v>
+      </c>
+      <c r="J459" t="n">
+        <v>315.35</v>
+      </c>
+      <c r="K459" t="n">
+        <v>285.29</v>
+      </c>
+      <c r="L459" t="n">
+        <v>313.92</v>
+      </c>
+      <c r="M459" t="n">
+        <v>317.19</v>
+      </c>
+      <c r="N459" t="n">
+        <v>309.06</v>
+      </c>
+      <c r="O459" t="n">
+        <v>294.38</v>
+      </c>
+      <c r="P459" t="n">
+        <v>292.22</v>
+      </c>
+      <c r="Q459" t="n">
+        <v>297.19</v>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -27836,7 +27896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B521"/>
+  <dimension ref="A1:B522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33049,6 +33109,16 @@
       </c>
       <c r="B521" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -33217,28 +33287,28 @@
         <v>0.1415</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7610174572375717</v>
+        <v>-0.7623110349665491</v>
       </c>
       <c r="J2" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K2" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0434144172998463</v>
+        <v>0.04374575336882813</v>
       </c>
       <c r="M2" t="n">
-        <v>22.09588972980953</v>
+        <v>22.05182274637016</v>
       </c>
       <c r="N2" t="n">
-        <v>715.2452126548998</v>
+        <v>713.6511365153432</v>
       </c>
       <c r="O2" t="n">
-        <v>26.74406873785101</v>
+        <v>26.71424969029344</v>
       </c>
       <c r="P2" t="n">
-        <v>287.2673138947977</v>
+        <v>287.2807389276834</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -33299,28 +33369,28 @@
         <v>0.119</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.734748312026471</v>
+        <v>-1.724217996669802</v>
       </c>
       <c r="J3" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K3" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2075831215903757</v>
+        <v>0.2060054658289027</v>
       </c>
       <c r="M3" t="n">
-        <v>19.79180748220382</v>
+        <v>19.7872536454751</v>
       </c>
       <c r="N3" t="n">
-        <v>647.0008488995747</v>
+        <v>646.9245332971306</v>
       </c>
       <c r="O3" t="n">
-        <v>25.43621137079134</v>
+        <v>25.43471118957576</v>
       </c>
       <c r="P3" t="n">
-        <v>331.4323271555822</v>
+        <v>331.3246204668371</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -33381,28 +33451,28 @@
         <v>0.0919</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.363680942898357</v>
+        <v>-1.356740070225822</v>
       </c>
       <c r="J4" t="n">
+        <v>458</v>
+      </c>
+      <c r="K4" t="n">
         <v>457</v>
       </c>
-      <c r="K4" t="n">
-        <v>456</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2434900013397765</v>
+        <v>0.2421265658664835</v>
       </c>
       <c r="M4" t="n">
-        <v>13.89309167424261</v>
+        <v>13.90185850030132</v>
       </c>
       <c r="N4" t="n">
-        <v>325.0053435351699</v>
+        <v>324.8829103754322</v>
       </c>
       <c r="O4" t="n">
-        <v>18.02790457971114</v>
+        <v>18.0245086028838</v>
       </c>
       <c r="P4" t="n">
-        <v>338.9533332647728</v>
+        <v>338.8821937109787</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33459,28 +33529,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.077933935977607</v>
+        <v>-1.070553792197885</v>
       </c>
       <c r="J5" t="n">
+        <v>458</v>
+      </c>
+      <c r="K5" t="n">
         <v>457</v>
       </c>
-      <c r="K5" t="n">
-        <v>456</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1936040064941876</v>
+        <v>0.1918018978625686</v>
       </c>
       <c r="M5" t="n">
-        <v>12.09658409461213</v>
+        <v>12.11215776549651</v>
       </c>
       <c r="N5" t="n">
-        <v>272.2386163528983</v>
+        <v>272.3085242288844</v>
       </c>
       <c r="O5" t="n">
-        <v>16.49965503739088</v>
+        <v>16.50177336618354</v>
       </c>
       <c r="P5" t="n">
-        <v>335.9200518924101</v>
+        <v>335.8444100876695</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33537,28 +33607,28 @@
         <v>0.0939</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9601408292829939</v>
+        <v>-0.9539016015499343</v>
       </c>
       <c r="J6" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K6" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1784651707549254</v>
+        <v>0.1769469897962718</v>
       </c>
       <c r="M6" t="n">
-        <v>11.23388424568635</v>
+        <v>11.24197720839552</v>
       </c>
       <c r="N6" t="n">
-        <v>235.3074681040524</v>
+        <v>235.2563371165606</v>
       </c>
       <c r="O6" t="n">
-        <v>15.33973494243145</v>
+        <v>15.33806823288254</v>
       </c>
       <c r="P6" t="n">
-        <v>336.3495266997061</v>
+        <v>336.2848947633331</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33615,28 +33685,28 @@
         <v>0.0557</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.969933202766982</v>
+        <v>-0.9638298360585787</v>
       </c>
       <c r="J7" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K7" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2014939896170719</v>
+        <v>0.1998666085281209</v>
       </c>
       <c r="M7" t="n">
-        <v>10.92310265968479</v>
+        <v>10.92968097733293</v>
       </c>
       <c r="N7" t="n">
-        <v>206.4338929003397</v>
+        <v>206.4260592492327</v>
       </c>
       <c r="O7" t="n">
-        <v>14.36780751890628</v>
+        <v>14.36753490509881</v>
       </c>
       <c r="P7" t="n">
-        <v>334.1766608212348</v>
+        <v>334.1134238547349</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33693,28 +33763,28 @@
         <v>0.056</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.48818776193087</v>
+        <v>-1.494024911220611</v>
       </c>
       <c r="J8" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K8" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L8" t="n">
-        <v>0.305135058632101</v>
+        <v>0.307465767410588</v>
       </c>
       <c r="M8" t="n">
-        <v>13.18437249747339</v>
+        <v>13.18887017543102</v>
       </c>
       <c r="N8" t="n">
-        <v>283.2896758921586</v>
+        <v>283.0865072121756</v>
       </c>
       <c r="O8" t="n">
-        <v>16.83121136140113</v>
+        <v>16.82517480480294</v>
       </c>
       <c r="P8" t="n">
-        <v>336.1934756325897</v>
+        <v>336.2533164266588</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33771,28 +33841,28 @@
         <v>0.0566</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.372672377169422</v>
+        <v>-1.37884071495648</v>
       </c>
       <c r="J9" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K9" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3219664103021078</v>
+        <v>0.3244767897577201</v>
       </c>
       <c r="M9" t="n">
-        <v>11.65485413605726</v>
+        <v>11.66147809232128</v>
       </c>
       <c r="N9" t="n">
-        <v>224.1793196536681</v>
+        <v>224.1542464123663</v>
       </c>
       <c r="O9" t="n">
-        <v>14.97261899781291</v>
+        <v>14.97178167127634</v>
       </c>
       <c r="P9" t="n">
-        <v>332.3181837872148</v>
+        <v>332.3812908167955</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33849,28 +33919,28 @@
         <v>0.0488</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.249188541859244</v>
+        <v>-1.241863855698547</v>
       </c>
       <c r="J10" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K10" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2367203492373459</v>
+        <v>0.2350130136366529</v>
       </c>
       <c r="M10" t="n">
-        <v>13.35726378135251</v>
+        <v>13.36252617748384</v>
       </c>
       <c r="N10" t="n">
-        <v>282.0264315597428</v>
+        <v>282.0608806541876</v>
       </c>
       <c r="O10" t="n">
-        <v>16.79364259354541</v>
+        <v>16.79466822102144</v>
       </c>
       <c r="P10" t="n">
-        <v>330.900455896002</v>
+        <v>330.8251401254566</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33927,28 +33997,28 @@
         <v>0.0619</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.386658812270453</v>
+        <v>-1.38893542616478</v>
       </c>
       <c r="J11" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K11" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2740314510546237</v>
+        <v>0.2755555107149442</v>
       </c>
       <c r="M11" t="n">
-        <v>12.95242188293644</v>
+        <v>12.9359598260783</v>
       </c>
       <c r="N11" t="n">
-        <v>287.2074923157045</v>
+        <v>286.6385609630383</v>
       </c>
       <c r="O11" t="n">
-        <v>16.94719718170838</v>
+        <v>16.93040344950581</v>
       </c>
       <c r="P11" t="n">
-        <v>327.1606703231955</v>
+        <v>327.1840247852934</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34005,28 +34075,28 @@
         <v>0.0561</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.039933210004328</v>
+        <v>-1.029225368510774</v>
       </c>
       <c r="J12" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K12" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1538001845272264</v>
+        <v>0.1511759450309218</v>
       </c>
       <c r="M12" t="n">
-        <v>14.48388239248066</v>
+        <v>14.50219077002451</v>
       </c>
       <c r="N12" t="n">
-        <v>332.6749893298904</v>
+        <v>333.3320036211716</v>
       </c>
       <c r="O12" t="n">
-        <v>18.23938017943292</v>
+        <v>18.25738216780192</v>
       </c>
       <c r="P12" t="n">
-        <v>316.1236098806912</v>
+        <v>316.0127950880685</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34083,28 +34153,28 @@
         <v>0.0425</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9337652414718893</v>
+        <v>-0.9241809654434687</v>
       </c>
       <c r="J13" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K13" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1418178365258922</v>
+        <v>0.1394202787124581</v>
       </c>
       <c r="M13" t="n">
-        <v>13.74405869572755</v>
+        <v>13.76790244167528</v>
       </c>
       <c r="N13" t="n">
-        <v>297.4098726908586</v>
+        <v>297.883159368136</v>
       </c>
       <c r="O13" t="n">
-        <v>17.24557545258663</v>
+        <v>17.25929197180858</v>
       </c>
       <c r="P13" t="n">
-        <v>319.0394218132796</v>
+        <v>318.9410838847225</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34161,28 +34231,28 @@
         <v>0.0451</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.289749484009025</v>
+        <v>-1.281191686496341</v>
       </c>
       <c r="J14" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K14" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1996632237803584</v>
+        <v>0.1978931082385033</v>
       </c>
       <c r="M14" t="n">
-        <v>15.31443483519156</v>
+        <v>15.32637204281962</v>
       </c>
       <c r="N14" t="n">
-        <v>375.5626050124151</v>
+        <v>375.6352026614957</v>
       </c>
       <c r="O14" t="n">
-        <v>19.37943768566093</v>
+        <v>19.38131065386177</v>
       </c>
       <c r="P14" t="n">
-        <v>322.706925652134</v>
+        <v>322.6191451783089</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34239,28 +34309,28 @@
         <v>0.0413</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.108212499633039</v>
+        <v>-1.104961964700818</v>
       </c>
       <c r="J15" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K15" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2148644907254182</v>
+        <v>0.214563003866463</v>
       </c>
       <c r="M15" t="n">
-        <v>12.46873240183197</v>
+        <v>12.4595528878424</v>
       </c>
       <c r="N15" t="n">
-        <v>252.3023393763301</v>
+        <v>251.8782014142327</v>
       </c>
       <c r="O15" t="n">
-        <v>15.88402780708754</v>
+        <v>15.87067110787167</v>
       </c>
       <c r="P15" t="n">
-        <v>315.8358197570424</v>
+        <v>315.802461758622</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -34321,28 +34391,28 @@
         <v>0.0337</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.685385097219453</v>
+        <v>-0.6837047945370116</v>
       </c>
       <c r="J16" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K16" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1076424320964936</v>
+        <v>0.107596589702979</v>
       </c>
       <c r="M16" t="n">
-        <v>11.61995892001269</v>
+        <v>11.60406752603056</v>
       </c>
       <c r="N16" t="n">
-        <v>219.3106003286302</v>
+        <v>218.8621803204813</v>
       </c>
       <c r="O16" t="n">
-        <v>14.80913908127782</v>
+        <v>14.79399135867266</v>
       </c>
       <c r="P16" t="n">
-        <v>306.2721213125771</v>
+        <v>306.2548696088767</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -34403,28 +34473,28 @@
         <v>0.1173</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2131541764168371</v>
+        <v>-0.2159529615291378</v>
       </c>
       <c r="J17" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K17" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01737540782667013</v>
+        <v>0.01789613754403963</v>
       </c>
       <c r="M17" t="n">
-        <v>7.927408138586999</v>
+        <v>7.927070848662936</v>
       </c>
       <c r="N17" t="n">
-        <v>142.2851963402508</v>
+        <v>142.0655051716227</v>
       </c>
       <c r="O17" t="n">
-        <v>11.92833585795817</v>
+        <v>11.91912350685329</v>
       </c>
       <c r="P17" t="n">
-        <v>309.3443115298738</v>
+        <v>309.3733562381113</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -34466,7 +34536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R458"/>
+  <dimension ref="A1:R459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76369,6 +76439,98 @@
         </is>
       </c>
     </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>-45.90668304094395,170.5516024771535</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>-45.90702419699121,170.55061725289647</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>-45.90707186675518,170.5496999338589</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>-45.90709073005535,170.54879647952365</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>-45.907072794942174,170.5478927825778</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>-45.90705943923722,170.54698990093834</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>-45.90671311597467,170.54609331402688</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>-45.90670963434913,170.545222041941</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>-45.906979261696286,170.544309514262</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>-45.90671513130745,170.5433986277188</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>-45.90699438663351,170.54250624335535</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>-45.907012930108564,170.5416135729664</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>-45.906935039082725,170.54070626485282</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>-45.90683341090598,170.53978569809027</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>-45.90686287144223,170.538858993332</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>-45.90700022649412,170.5379620768486</t>
+        </is>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0510/nzd0510.xlsx
+++ b/data/nzd0510/nzd0510.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R459"/>
+  <dimension ref="A1:R460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27880,6 +27880,66 @@
         <v>297.19</v>
       </c>
       <c r="R459" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>285.13</v>
+      </c>
+      <c r="C460" t="n">
+        <v>310.63</v>
+      </c>
+      <c r="D460" t="n">
+        <v>319.54</v>
+      </c>
+      <c r="E460" t="n">
+        <v>325.06</v>
+      </c>
+      <c r="F460" t="n">
+        <v>330.49</v>
+      </c>
+      <c r="G460" t="n">
+        <v>326.04</v>
+      </c>
+      <c r="H460" t="n">
+        <v>315.42</v>
+      </c>
+      <c r="I460" t="n">
+        <v>303.8</v>
+      </c>
+      <c r="J460" t="n">
+        <v>318.85</v>
+      </c>
+      <c r="K460" t="n">
+        <v>310.65</v>
+      </c>
+      <c r="L460" t="n">
+        <v>317.1</v>
+      </c>
+      <c r="M460" t="n">
+        <v>323.79</v>
+      </c>
+      <c r="N460" t="n">
+        <v>319.62</v>
+      </c>
+      <c r="O460" t="n">
+        <v>301.84</v>
+      </c>
+      <c r="P460" t="n">
+        <v>295.88</v>
+      </c>
+      <c r="Q460" t="n">
+        <v>303.34</v>
+      </c>
+      <c r="R460" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -27896,7 +27956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B522"/>
+  <dimension ref="A1:B523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33119,6 +33179,16 @@
       </c>
       <c r="B522" t="n">
         <v>0.25</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>-0.19</v>
       </c>
     </row>
   </sheetData>
@@ -33287,28 +33357,28 @@
         <v>0.1415</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7623110349665491</v>
+        <v>-0.7546337593575719</v>
       </c>
       <c r="J2" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K2" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04374575336882813</v>
+        <v>0.04305400492297329</v>
       </c>
       <c r="M2" t="n">
-        <v>22.05182274637016</v>
+        <v>22.04827959662335</v>
       </c>
       <c r="N2" t="n">
-        <v>713.6511365153432</v>
+        <v>712.7646814457383</v>
       </c>
       <c r="O2" t="n">
-        <v>26.71424969029344</v>
+        <v>26.69765310745007</v>
       </c>
       <c r="P2" t="n">
-        <v>287.2807389276834</v>
+        <v>287.20082459811</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -33369,28 +33439,28 @@
         <v>0.119</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.724217996669802</v>
+        <v>-1.713724828972248</v>
       </c>
       <c r="J3" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K3" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2060054658289027</v>
+        <v>0.204435857433228</v>
       </c>
       <c r="M3" t="n">
-        <v>19.7872536454751</v>
+        <v>19.78282032076419</v>
       </c>
       <c r="N3" t="n">
-        <v>646.9245332971306</v>
+        <v>646.8419840789782</v>
       </c>
       <c r="O3" t="n">
-        <v>25.43471118957576</v>
+        <v>25.43308837084042</v>
       </c>
       <c r="P3" t="n">
-        <v>331.3246204668371</v>
+        <v>331.2169812517898</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -33451,28 +33521,28 @@
         <v>0.0919</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.356740070225822</v>
+        <v>-1.349817252585062</v>
       </c>
       <c r="J4" t="n">
+        <v>459</v>
+      </c>
+      <c r="K4" t="n">
         <v>458</v>
       </c>
-      <c r="K4" t="n">
-        <v>457</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2421265658664835</v>
+        <v>0.2407674691573514</v>
       </c>
       <c r="M4" t="n">
-        <v>13.90185850030132</v>
+        <v>13.91038025723369</v>
       </c>
       <c r="N4" t="n">
-        <v>324.8829103754322</v>
+        <v>324.7591526557337</v>
       </c>
       <c r="O4" t="n">
-        <v>18.0245086028838</v>
+        <v>18.021075235838</v>
       </c>
       <c r="P4" t="n">
-        <v>338.8821937109787</v>
+        <v>338.8110322622267</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33529,28 +33599,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.070553792197885</v>
+        <v>-1.063202716068097</v>
       </c>
       <c r="J5" t="n">
+        <v>459</v>
+      </c>
+      <c r="K5" t="n">
         <v>458</v>
       </c>
-      <c r="K5" t="n">
-        <v>457</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1918018978625686</v>
+        <v>0.1900113308560206</v>
       </c>
       <c r="M5" t="n">
-        <v>12.11215776549651</v>
+        <v>12.12757756030689</v>
       </c>
       <c r="N5" t="n">
-        <v>272.3085242288844</v>
+        <v>272.3742505880602</v>
       </c>
       <c r="O5" t="n">
-        <v>16.50177336618354</v>
+        <v>16.50376473984225</v>
       </c>
       <c r="P5" t="n">
-        <v>335.8444100876695</v>
+        <v>335.7688464581725</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33607,28 +33677,28 @@
         <v>0.0939</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9539016015499343</v>
+        <v>-0.9456441468819912</v>
       </c>
       <c r="J6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K6" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1769469897962718</v>
+        <v>0.1745978556304535</v>
       </c>
       <c r="M6" t="n">
-        <v>11.24197720839552</v>
+        <v>11.26051989346308</v>
       </c>
       <c r="N6" t="n">
-        <v>235.2563371165606</v>
+        <v>235.5565878047038</v>
       </c>
       <c r="O6" t="n">
-        <v>15.33806823288254</v>
+        <v>15.3478528727866</v>
       </c>
       <c r="P6" t="n">
-        <v>336.2848947633331</v>
+        <v>336.1991097006547</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33685,28 +33755,28 @@
         <v>0.0557</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9638298360585787</v>
+        <v>-0.956430419020347</v>
       </c>
       <c r="J7" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K7" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1998666085281209</v>
+        <v>0.1976476833193176</v>
       </c>
       <c r="M7" t="n">
-        <v>10.92968097733293</v>
+        <v>10.94312669606397</v>
       </c>
       <c r="N7" t="n">
-        <v>206.4260592492327</v>
+        <v>206.62814209357</v>
       </c>
       <c r="O7" t="n">
-        <v>14.36753490509881</v>
+        <v>14.37456580539287</v>
       </c>
       <c r="P7" t="n">
-        <v>334.1134238547349</v>
+        <v>334.0365384397263</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33763,28 +33833,28 @@
         <v>0.056</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.494024911220611</v>
+        <v>-1.486206069278991</v>
       </c>
       <c r="J8" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K8" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L8" t="n">
-        <v>0.307465767410588</v>
+        <v>0.3056569335561727</v>
       </c>
       <c r="M8" t="n">
-        <v>13.18887017543102</v>
+        <v>13.19623117271033</v>
       </c>
       <c r="N8" t="n">
-        <v>283.0865072121756</v>
+        <v>283.2149370481821</v>
       </c>
       <c r="O8" t="n">
-        <v>16.82517480480294</v>
+        <v>16.82899096940105</v>
       </c>
       <c r="P8" t="n">
-        <v>336.2533164266588</v>
+        <v>336.1729268970365</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33841,28 +33911,28 @@
         <v>0.0566</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.37884071495648</v>
+        <v>-1.375566112184403</v>
       </c>
       <c r="J9" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K9" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3244767897577201</v>
+        <v>0.324315629089922</v>
       </c>
       <c r="M9" t="n">
-        <v>11.66147809232128</v>
+        <v>11.65281665481794</v>
       </c>
       <c r="N9" t="n">
-        <v>224.1542464123663</v>
+        <v>223.7944492091655</v>
       </c>
       <c r="O9" t="n">
-        <v>14.97178167127634</v>
+        <v>14.95976100107102</v>
       </c>
       <c r="P9" t="n">
-        <v>332.3812908167955</v>
+        <v>332.3476905582063</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33919,28 +33989,28 @@
         <v>0.0488</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.241863855698547</v>
+        <v>-1.233084954861238</v>
       </c>
       <c r="J10" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K10" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2350130136366529</v>
+        <v>0.2327023355894924</v>
       </c>
       <c r="M10" t="n">
-        <v>13.36252617748384</v>
+        <v>13.37459992613799</v>
       </c>
       <c r="N10" t="n">
-        <v>282.0608806541876</v>
+        <v>282.3814480942691</v>
       </c>
       <c r="O10" t="n">
-        <v>16.79466822102144</v>
+        <v>16.8042092373985</v>
       </c>
       <c r="P10" t="n">
-        <v>330.8251401254566</v>
+        <v>330.7346086064393</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33997,28 +34067,28 @@
         <v>0.0619</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.38893542616478</v>
+        <v>-1.380466864528154</v>
       </c>
       <c r="J11" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K11" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2755555107149442</v>
+        <v>0.273423413779189</v>
       </c>
       <c r="M11" t="n">
-        <v>12.9359598260783</v>
+        <v>12.95103873045937</v>
       </c>
       <c r="N11" t="n">
-        <v>286.6385609630383</v>
+        <v>286.8896031876256</v>
       </c>
       <c r="O11" t="n">
-        <v>16.93040344950581</v>
+        <v>16.93781577381291</v>
       </c>
       <c r="P11" t="n">
-        <v>327.1840247852934</v>
+        <v>327.0968950965909</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34075,28 +34145,28 @@
         <v>0.0561</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.029225368510774</v>
+        <v>-1.017221804366363</v>
       </c>
       <c r="J12" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K12" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1511759450309218</v>
+        <v>0.1481068919343022</v>
       </c>
       <c r="M12" t="n">
-        <v>14.50219077002451</v>
+        <v>14.52656456125728</v>
       </c>
       <c r="N12" t="n">
-        <v>333.3320036211716</v>
+        <v>334.3470832217168</v>
       </c>
       <c r="O12" t="n">
-        <v>18.25738216780192</v>
+        <v>18.28516019130587</v>
       </c>
       <c r="P12" t="n">
-        <v>316.0127950880685</v>
+        <v>315.8882055931473</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34153,28 +34223,28 @@
         <v>0.0425</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9241809654434687</v>
+        <v>-0.9118640583218569</v>
       </c>
       <c r="J13" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K13" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1394202787124581</v>
+        <v>0.1360379444544189</v>
       </c>
       <c r="M13" t="n">
-        <v>13.76790244167528</v>
+        <v>13.80755524432144</v>
       </c>
       <c r="N13" t="n">
-        <v>297.883159368136</v>
+        <v>299.0916267399544</v>
       </c>
       <c r="O13" t="n">
-        <v>17.25929197180858</v>
+        <v>17.29426571843842</v>
       </c>
       <c r="P13" t="n">
-        <v>318.9410838847225</v>
+        <v>318.8143364551477</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34231,28 +34301,28 @@
         <v>0.0451</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.281191686496341</v>
+        <v>-1.268217446228957</v>
       </c>
       <c r="J14" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K14" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1978931082385033</v>
+        <v>0.1945430203975996</v>
       </c>
       <c r="M14" t="n">
-        <v>15.32637204281962</v>
+        <v>15.36154893376719</v>
       </c>
       <c r="N14" t="n">
-        <v>375.6352026614957</v>
+        <v>376.8751117535967</v>
       </c>
       <c r="O14" t="n">
-        <v>19.38131065386177</v>
+        <v>19.4132715365957</v>
       </c>
       <c r="P14" t="n">
-        <v>322.6191451783089</v>
+        <v>322.4856732697135</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34309,28 +34379,28 @@
         <v>0.0413</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.104961964700818</v>
+        <v>-1.098564610584396</v>
       </c>
       <c r="J15" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K15" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L15" t="n">
-        <v>0.214563003866463</v>
+        <v>0.2130519222840164</v>
       </c>
       <c r="M15" t="n">
-        <v>12.4595528878424</v>
+        <v>12.46806588800139</v>
       </c>
       <c r="N15" t="n">
-        <v>251.8782014142327</v>
+        <v>251.8272347474909</v>
       </c>
       <c r="O15" t="n">
-        <v>15.87067110787167</v>
+        <v>15.86906533944236</v>
       </c>
       <c r="P15" t="n">
-        <v>315.802461758622</v>
+        <v>315.7366183119278</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -34391,28 +34461,28 @@
         <v>0.0337</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6837047945370116</v>
+        <v>-0.6804785119500663</v>
       </c>
       <c r="J16" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K16" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L16" t="n">
-        <v>0.107596589702979</v>
+        <v>0.1070751330047168</v>
       </c>
       <c r="M16" t="n">
-        <v>11.60406752603056</v>
+        <v>11.5970636202753</v>
       </c>
       <c r="N16" t="n">
-        <v>218.8621803204813</v>
+        <v>218.5088541196315</v>
       </c>
       <c r="O16" t="n">
-        <v>14.79399135867266</v>
+        <v>14.78204499112459</v>
       </c>
       <c r="P16" t="n">
-        <v>306.2548696088767</v>
+        <v>306.2216479353003</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -34473,28 +34543,28 @@
         <v>0.1173</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2159529615291378</v>
+        <v>-0.2160978021238497</v>
       </c>
       <c r="J17" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K17" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01789613754403963</v>
+        <v>0.01800155410341608</v>
       </c>
       <c r="M17" t="n">
-        <v>7.927070848662936</v>
+        <v>7.91052811456366</v>
       </c>
       <c r="N17" t="n">
-        <v>142.0655051716227</v>
+        <v>141.7535242273033</v>
       </c>
       <c r="O17" t="n">
-        <v>11.91912350685329</v>
+        <v>11.90602890250579</v>
       </c>
       <c r="P17" t="n">
-        <v>309.3733562381113</v>
+        <v>309.3748636717871</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -34536,7 +34606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R459"/>
+  <dimension ref="A1:R460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76531,6 +76601,98 @@
         </is>
       </c>
     </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>-45.90686932845309,170.55156592623436</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>-45.90702419699121,170.55061725289647</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>-45.90707186675518,170.5496999338589</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>-45.90709073005535,170.54879647952365</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>-45.907115867280666,170.5478908628059</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>-45.9070872382469,170.54698977781973</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>-45.90700289132075,170.54609202750598</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>-45.90690947135573,170.54521077376768</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>-45.907010719656554,170.54430755528546</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>-45.906943281713055,170.5433990574157</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>-45.90702299327075,170.5425057417897</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>-45.90707227320221,170.54161071197697</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>-45.90703004169585,170.5407061041663</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>-45.90690046943234,170.53978959250762</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>-45.90689566469286,170.5388632409971</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>-45.9070551151129,170.53797204772857</t>
+        </is>
+      </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0510/nzd0510.xlsx
+++ b/data/nzd0510/nzd0510.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R460"/>
+  <dimension ref="A1:R461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27895,13 +27895,13 @@
         <v>285.13</v>
       </c>
       <c r="C460" t="n">
-        <v>310.63</v>
+        <v>318.29</v>
       </c>
       <c r="D460" t="n">
-        <v>319.54</v>
+        <v>325.45</v>
       </c>
       <c r="E460" t="n">
-        <v>325.06</v>
+        <v>329.68</v>
       </c>
       <c r="F460" t="n">
         <v>330.49</v>
@@ -27913,7 +27913,7 @@
         <v>315.42</v>
       </c>
       <c r="I460" t="n">
-        <v>303.8</v>
+        <v>309.79</v>
       </c>
       <c r="J460" t="n">
         <v>318.85</v>
@@ -27940,6 +27940,66 @@
         <v>303.34</v>
       </c>
       <c r="R460" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:48+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="C461" t="n">
+        <v>322.85</v>
+      </c>
+      <c r="D461" t="n">
+        <v>327.81</v>
+      </c>
+      <c r="E461" t="n">
+        <v>331.83</v>
+      </c>
+      <c r="F461" t="n">
+        <v>332.67</v>
+      </c>
+      <c r="G461" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="H461" t="n">
+        <v>327.1</v>
+      </c>
+      <c r="I461" t="n">
+        <v>320.8</v>
+      </c>
+      <c r="J461" t="n">
+        <v>318.23</v>
+      </c>
+      <c r="K461" t="n">
+        <v>312.19</v>
+      </c>
+      <c r="L461" t="n">
+        <v>318.31</v>
+      </c>
+      <c r="M461" t="n">
+        <v>324.26</v>
+      </c>
+      <c r="N461" t="n">
+        <v>319.46</v>
+      </c>
+      <c r="O461" t="n">
+        <v>303.52</v>
+      </c>
+      <c r="P461" t="n">
+        <v>299.06</v>
+      </c>
+      <c r="Q461" t="n">
+        <v>304.72</v>
+      </c>
+      <c r="R461" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -27956,7 +28016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B523"/>
+  <dimension ref="A1:B524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33189,6 +33249,16 @@
       </c>
       <c r="B523" t="n">
         <v>-0.19</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -33357,28 +33427,28 @@
         <v>0.1415</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7546337593575719</v>
+        <v>-0.7402071765102676</v>
       </c>
       <c r="J2" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K2" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04305400492297329</v>
+        <v>0.04153385605546178</v>
       </c>
       <c r="M2" t="n">
-        <v>22.04827959662335</v>
+        <v>22.08534549720228</v>
       </c>
       <c r="N2" t="n">
-        <v>712.7646814457383</v>
+        <v>713.6961300171719</v>
       </c>
       <c r="O2" t="n">
-        <v>26.69765310745007</v>
+        <v>26.71509180252188</v>
       </c>
       <c r="P2" t="n">
-        <v>287.20082459811</v>
+        <v>287.0500378870151</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -33439,28 +33509,28 @@
         <v>0.119</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.713724828972248</v>
+        <v>-1.694821010271865</v>
       </c>
       <c r="J3" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K3" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L3" t="n">
-        <v>0.204435857433228</v>
+        <v>0.2006330221136163</v>
       </c>
       <c r="M3" t="n">
-        <v>19.78282032076419</v>
+        <v>19.81082776280173</v>
       </c>
       <c r="N3" t="n">
-        <v>646.8419840789782</v>
+        <v>649.3410291721931</v>
       </c>
       <c r="O3" t="n">
-        <v>25.43308837084042</v>
+        <v>25.48217080965028</v>
       </c>
       <c r="P3" t="n">
-        <v>331.2169812517898</v>
+        <v>331.0224209999897</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -33521,28 +33591,28 @@
         <v>0.0919</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.349817252585062</v>
+        <v>-1.336924901098851</v>
       </c>
       <c r="J4" t="n">
+        <v>460</v>
+      </c>
+      <c r="K4" t="n">
         <v>459</v>
       </c>
-      <c r="K4" t="n">
-        <v>458</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2407674691573514</v>
+        <v>0.2371082206513785</v>
       </c>
       <c r="M4" t="n">
-        <v>13.91038025723369</v>
+        <v>13.95187194357795</v>
       </c>
       <c r="N4" t="n">
-        <v>324.7591526557337</v>
+        <v>325.8637746618083</v>
       </c>
       <c r="O4" t="n">
-        <v>18.021075235838</v>
+        <v>18.0516972792535</v>
       </c>
       <c r="P4" t="n">
-        <v>338.8110322622267</v>
+        <v>338.6780786981979</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33599,28 +33669,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.063202716068097</v>
+        <v>-1.051070532252451</v>
       </c>
       <c r="J5" t="n">
+        <v>460</v>
+      </c>
+      <c r="K5" t="n">
         <v>459</v>
       </c>
-      <c r="K5" t="n">
-        <v>458</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1900113308560206</v>
+        <v>0.1862868021834572</v>
       </c>
       <c r="M5" t="n">
-        <v>12.12757756030689</v>
+        <v>12.16994947027998</v>
       </c>
       <c r="N5" t="n">
-        <v>272.3742505880602</v>
+        <v>273.4379116983678</v>
       </c>
       <c r="O5" t="n">
-        <v>16.50376473984225</v>
+        <v>16.53595814273753</v>
       </c>
       <c r="P5" t="n">
-        <v>335.7688464581725</v>
+        <v>335.6437158189558</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33677,28 +33747,28 @@
         <v>0.0939</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9456441468819912</v>
+        <v>-0.9364680840912898</v>
       </c>
       <c r="J6" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K6" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1745978556304535</v>
+        <v>0.1718646647387225</v>
       </c>
       <c r="M6" t="n">
-        <v>11.26051989346308</v>
+        <v>11.28410789178136</v>
       </c>
       <c r="N6" t="n">
-        <v>235.5565878047038</v>
+        <v>236.0443904133294</v>
       </c>
       <c r="O6" t="n">
-        <v>15.3478528727866</v>
+        <v>15.36373621269675</v>
       </c>
       <c r="P6" t="n">
-        <v>336.1991097006547</v>
+        <v>336.1034031341559</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33755,28 +33825,28 @@
         <v>0.0557</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.956430419020347</v>
+        <v>-0.9479858827473366</v>
       </c>
       <c r="J7" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K7" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1976476833193176</v>
+        <v>0.19494086932924</v>
       </c>
       <c r="M7" t="n">
-        <v>10.94312669606397</v>
+        <v>10.96178943665124</v>
       </c>
       <c r="N7" t="n">
-        <v>206.62814209357</v>
+        <v>207.0246184716223</v>
       </c>
       <c r="O7" t="n">
-        <v>14.37456580539287</v>
+        <v>14.38835009553292</v>
       </c>
       <c r="P7" t="n">
-        <v>334.0365384397263</v>
+        <v>333.9484464670019</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33833,28 +33903,28 @@
         <v>0.056</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.486206069278991</v>
+        <v>-1.473448683542048</v>
       </c>
       <c r="J8" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K8" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3056569335561727</v>
+        <v>0.3015229880442488</v>
       </c>
       <c r="M8" t="n">
-        <v>13.19623117271033</v>
+        <v>13.22587274246065</v>
       </c>
       <c r="N8" t="n">
-        <v>283.2149370481821</v>
+        <v>284.5740749720727</v>
       </c>
       <c r="O8" t="n">
-        <v>16.82899096940105</v>
+        <v>16.86932348886797</v>
       </c>
       <c r="P8" t="n">
-        <v>336.1729268970365</v>
+        <v>336.0412364360398</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33911,28 +33981,28 @@
         <v>0.0566</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.375566112184403</v>
+        <v>-1.36259149538277</v>
       </c>
       <c r="J9" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K9" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L9" t="n">
-        <v>0.324315629089922</v>
+        <v>0.3196160405521318</v>
       </c>
       <c r="M9" t="n">
-        <v>11.65281665481794</v>
+        <v>11.6937848213847</v>
       </c>
       <c r="N9" t="n">
-        <v>223.7944492091655</v>
+        <v>224.9218385510254</v>
       </c>
       <c r="O9" t="n">
-        <v>14.95976100107102</v>
+        <v>14.99739439206109</v>
       </c>
       <c r="P9" t="n">
-        <v>332.3476905582063</v>
+        <v>332.2141255308069</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33989,28 +34059,28 @@
         <v>0.0488</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.233084954861238</v>
+        <v>-1.224574431537746</v>
       </c>
       <c r="J10" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K10" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2327023355894924</v>
+        <v>0.2305117013228924</v>
       </c>
       <c r="M10" t="n">
-        <v>13.37459992613799</v>
+        <v>13.38520378704193</v>
       </c>
       <c r="N10" t="n">
-        <v>282.3814480942691</v>
+        <v>282.642172738086</v>
       </c>
       <c r="O10" t="n">
-        <v>16.8042092373985</v>
+        <v>16.81196516585988</v>
       </c>
       <c r="P10" t="n">
-        <v>330.7346086064393</v>
+        <v>330.646492655515</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34067,28 +34137,28 @@
         <v>0.0619</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.380466864528154</v>
+        <v>-1.371344599963771</v>
       </c>
       <c r="J11" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K11" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L11" t="n">
-        <v>0.273423413779189</v>
+        <v>0.2710113975708215</v>
       </c>
       <c r="M11" t="n">
-        <v>12.95103873045937</v>
+        <v>12.96990412781817</v>
       </c>
       <c r="N11" t="n">
-        <v>286.8896031876256</v>
+        <v>287.2780217586287</v>
       </c>
       <c r="O11" t="n">
-        <v>16.93781577381291</v>
+        <v>16.94927791260232</v>
       </c>
       <c r="P11" t="n">
-        <v>327.0968950965909</v>
+        <v>327.0026592950122</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34145,28 +34215,28 @@
         <v>0.0561</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.017221804366363</v>
+        <v>-1.004729858127691</v>
       </c>
       <c r="J12" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K12" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1481068919343022</v>
+        <v>0.1448900365858844</v>
       </c>
       <c r="M12" t="n">
-        <v>14.52656456125728</v>
+        <v>14.55352665046219</v>
       </c>
       <c r="N12" t="n">
-        <v>334.3470832217168</v>
+        <v>335.4982231664372</v>
       </c>
       <c r="O12" t="n">
-        <v>18.28516019130587</v>
+        <v>18.31661058073893</v>
       </c>
       <c r="P12" t="n">
-        <v>315.8882055931473</v>
+        <v>315.758021759462</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34223,28 +34293,28 @@
         <v>0.0425</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9118640583218569</v>
+        <v>-0.8993840111588729</v>
       </c>
       <c r="J13" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K13" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1360379444544189</v>
+        <v>0.1326322654698178</v>
       </c>
       <c r="M13" t="n">
-        <v>13.80755524432144</v>
+        <v>13.84797099726266</v>
       </c>
       <c r="N13" t="n">
-        <v>299.0916267399544</v>
+        <v>300.3397300379007</v>
       </c>
       <c r="O13" t="n">
-        <v>17.29426571843842</v>
+        <v>17.33031246221201</v>
       </c>
       <c r="P13" t="n">
-        <v>318.8143364551477</v>
+        <v>318.6853897938428</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34301,28 +34371,28 @@
         <v>0.0451</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.268217446228957</v>
+        <v>-1.255335796369796</v>
       </c>
       <c r="J14" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K14" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1945430203975996</v>
+        <v>0.1912502128467836</v>
       </c>
       <c r="M14" t="n">
-        <v>15.36154893376719</v>
+        <v>15.3961467097826</v>
       </c>
       <c r="N14" t="n">
-        <v>376.8751117535967</v>
+        <v>378.0754164646009</v>
       </c>
       <c r="O14" t="n">
-        <v>19.4132715365957</v>
+        <v>19.44416150068192</v>
       </c>
       <c r="P14" t="n">
-        <v>322.4856732697135</v>
+        <v>322.3526184176844</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34379,28 +34449,28 @@
         <v>0.0413</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.098564610584396</v>
+        <v>-1.091452564577885</v>
       </c>
       <c r="J15" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K15" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2130519222840164</v>
+        <v>0.2112481683473598</v>
       </c>
       <c r="M15" t="n">
-        <v>12.46806588800139</v>
+        <v>12.48071734807879</v>
       </c>
       <c r="N15" t="n">
-        <v>251.8272347474909</v>
+        <v>251.8927572114081</v>
       </c>
       <c r="O15" t="n">
-        <v>15.86906533944236</v>
+        <v>15.87112967659858</v>
       </c>
       <c r="P15" t="n">
-        <v>315.7366183119278</v>
+        <v>315.6631244321037</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -34461,28 +34531,28 @@
         <v>0.0337</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6804785119500663</v>
+        <v>-0.6758988447249987</v>
       </c>
       <c r="J16" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K16" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1070751330047168</v>
+        <v>0.1061185336775526</v>
       </c>
       <c r="M16" t="n">
-        <v>11.5970636202753</v>
+        <v>11.59765703935564</v>
       </c>
       <c r="N16" t="n">
-        <v>218.5088541196315</v>
+        <v>218.2857665775336</v>
       </c>
       <c r="O16" t="n">
-        <v>14.78204499112459</v>
+        <v>14.77449716834836</v>
       </c>
       <c r="P16" t="n">
-        <v>306.2216479353003</v>
+        <v>306.1742992565582</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -34543,28 +34613,28 @@
         <v>0.1173</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2160978021238497</v>
+        <v>-0.2156447272339416</v>
       </c>
       <c r="J17" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K17" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01800155410341608</v>
+        <v>0.01800967698975653</v>
       </c>
       <c r="M17" t="n">
-        <v>7.91052811456366</v>
+        <v>7.895070898023206</v>
       </c>
       <c r="N17" t="n">
-        <v>141.7535242273033</v>
+        <v>141.445105312031</v>
       </c>
       <c r="O17" t="n">
-        <v>11.90602890250579</v>
+        <v>11.89306963369974</v>
       </c>
       <c r="P17" t="n">
-        <v>309.3748636717871</v>
+        <v>309.3701295487895</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -34606,7 +34676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R460"/>
+  <dimension ref="A1:R461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76614,17 +76684,17 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>-45.90702419699121,170.55061725289647</t>
+          <t>-45.90709273723022,170.55060699683312</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>-45.90707186675518,170.5496999338589</t>
+          <t>-45.907124901744346,170.54969452395724</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>-45.90709073005535,170.54879647952365</t>
+          <t>-45.90713220704706,170.548792633642</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
@@ -76644,7 +76714,7 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>-45.90690947135573,170.54521077376768</t>
+          <t>-45.906963318572764,170.54520773747532</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
@@ -76688,6 +76758,98 @@
         </is>
       </c>
       <c r="R460" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:48+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>-45.90701015822996,170.55153829425984</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>-45.907133539251376,170.5506008913823</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>-45.90714607984468,170.54969236365463</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-45.90715150911013,170.54879084388946</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>-45.90713547014025,170.5478899890878</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>-45.907109369497206,170.54698967980246</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>-45.90710796974153,170.54609156096865</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>-45.90706229317199,170.54520215655643</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>-45.90700514710361,170.54430790230438</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>-45.906957136272126,170.54339908350815</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>-45.90703387818615,170.5425055509421</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>-45.90707649914976,170.54161050823953</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>-45.907028602262336,170.540706106601</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>-45.906915571084284,170.5397904695354</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>-45.90692415718913,170.53886693159475</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>-45.90706743158332,170.53797428509915</t>
+        </is>
+      </c>
+      <c r="R461" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0510/nzd0510.xlsx
+++ b/data/nzd0510/nzd0510.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R461"/>
+  <dimension ref="A1:R462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28002,6 +28002,66 @@
       <c r="R461" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:42+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>349.86</v>
+      </c>
+      <c r="C462" t="n">
+        <v>338.85</v>
+      </c>
+      <c r="D462" t="n">
+        <v>338.52</v>
+      </c>
+      <c r="E462" t="n">
+        <v>340.86</v>
+      </c>
+      <c r="F462" t="n">
+        <v>337.37</v>
+      </c>
+      <c r="G462" t="n">
+        <v>335.81</v>
+      </c>
+      <c r="H462" t="n">
+        <v>338.54</v>
+      </c>
+      <c r="I462" t="n">
+        <v>333.97</v>
+      </c>
+      <c r="J462" t="n">
+        <v>321.07</v>
+      </c>
+      <c r="K462" t="n">
+        <v>329.37</v>
+      </c>
+      <c r="L462" t="n">
+        <v>327.19</v>
+      </c>
+      <c r="M462" t="n">
+        <v>332.47</v>
+      </c>
+      <c r="N462" t="n">
+        <v>326.79</v>
+      </c>
+      <c r="O462" t="n">
+        <v>315.82</v>
+      </c>
+      <c r="P462" t="n">
+        <v>309.82</v>
+      </c>
+      <c r="Q462" t="n">
+        <v>317.31</v>
+      </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28016,7 +28076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B524"/>
+  <dimension ref="A1:B525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33259,6 +33319,16 @@
       </c>
       <c r="B524" t="n">
         <v>0.34</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>-0.93</v>
       </c>
     </row>
   </sheetData>
@@ -33427,28 +33497,28 @@
         <v>0.1415</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7402071765102676</v>
+        <v>-0.7047760616464955</v>
       </c>
       <c r="J2" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K2" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04153385605546178</v>
+        <v>0.03720867915652681</v>
       </c>
       <c r="M2" t="n">
-        <v>22.08534549720228</v>
+        <v>22.24873272446845</v>
       </c>
       <c r="N2" t="n">
-        <v>713.6961300171719</v>
+        <v>727.2428892820952</v>
       </c>
       <c r="O2" t="n">
-        <v>26.71509180252188</v>
+        <v>26.96744128170293</v>
       </c>
       <c r="P2" t="n">
-        <v>287.0500378870151</v>
+        <v>286.6778376378032</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -33509,28 +33579,28 @@
         <v>0.119</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.694821010271865</v>
+        <v>-1.672337598755424</v>
       </c>
       <c r="J3" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K3" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2006330221136163</v>
+        <v>0.1956634774380676</v>
       </c>
       <c r="M3" t="n">
-        <v>19.81082776280173</v>
+        <v>19.85162093758423</v>
       </c>
       <c r="N3" t="n">
-        <v>649.3410291721931</v>
+        <v>653.9805377927016</v>
       </c>
       <c r="O3" t="n">
-        <v>25.48217080965028</v>
+        <v>25.57304318599375</v>
       </c>
       <c r="P3" t="n">
-        <v>331.0224209999897</v>
+        <v>330.7897166204515</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -33591,28 +33661,28 @@
         <v>0.0919</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.336924901098851</v>
+        <v>-1.321966050264917</v>
       </c>
       <c r="J4" t="n">
+        <v>461</v>
+      </c>
+      <c r="K4" t="n">
         <v>460</v>
       </c>
-      <c r="K4" t="n">
-        <v>459</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2371082206513785</v>
+        <v>0.2324243735394671</v>
       </c>
       <c r="M4" t="n">
-        <v>13.95187194357795</v>
+        <v>14.00376053225433</v>
       </c>
       <c r="N4" t="n">
-        <v>325.8637746618083</v>
+        <v>327.854528246378</v>
       </c>
       <c r="O4" t="n">
-        <v>18.0516972792535</v>
+        <v>18.10675366393374</v>
       </c>
       <c r="P4" t="n">
-        <v>338.6780786981979</v>
+        <v>338.522931184372</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33669,28 +33739,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.051070532252451</v>
+        <v>-1.037052786129342</v>
       </c>
       <c r="J5" t="n">
+        <v>461</v>
+      </c>
+      <c r="K5" t="n">
         <v>460</v>
       </c>
-      <c r="K5" t="n">
-        <v>459</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1862868021834572</v>
+        <v>0.1816624748176764</v>
       </c>
       <c r="M5" t="n">
-        <v>12.16994947027998</v>
+        <v>12.22203219263745</v>
       </c>
       <c r="N5" t="n">
-        <v>273.4379116983678</v>
+        <v>275.2136947815877</v>
       </c>
       <c r="O5" t="n">
-        <v>16.53595814273753</v>
+        <v>16.58956584065983</v>
       </c>
       <c r="P5" t="n">
-        <v>335.6437158189558</v>
+        <v>335.4983290854033</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33747,28 +33817,28 @@
         <v>0.0939</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9364680840912898</v>
+        <v>-0.9252670318748046</v>
       </c>
       <c r="J6" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K6" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1718646647387225</v>
+        <v>0.1682499788117483</v>
       </c>
       <c r="M6" t="n">
-        <v>11.28410789178136</v>
+        <v>11.31854105782268</v>
       </c>
       <c r="N6" t="n">
-        <v>236.0443904133294</v>
+        <v>237.0114114623676</v>
       </c>
       <c r="O6" t="n">
-        <v>15.36373621269675</v>
+        <v>15.39517494094717</v>
       </c>
       <c r="P6" t="n">
-        <v>336.1034031341559</v>
+        <v>335.9860051150126</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33825,28 +33895,28 @@
         <v>0.0557</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9479858827473366</v>
+        <v>-0.9363967110925796</v>
       </c>
       <c r="J7" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K7" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L7" t="n">
-        <v>0.19494086932924</v>
+        <v>0.1906608749794406</v>
       </c>
       <c r="M7" t="n">
-        <v>10.96178943665124</v>
+        <v>10.99669149224231</v>
       </c>
       <c r="N7" t="n">
-        <v>207.0246184716223</v>
+        <v>208.1567404804983</v>
       </c>
       <c r="O7" t="n">
-        <v>14.38835009553292</v>
+        <v>14.42763807698607</v>
       </c>
       <c r="P7" t="n">
-        <v>333.9484464670019</v>
+        <v>333.8269615317453</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33903,28 +33973,28 @@
         <v>0.056</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.473448683542048</v>
+        <v>-1.455828407047184</v>
       </c>
       <c r="J8" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K8" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3015229880442488</v>
+        <v>0.2947373575351261</v>
       </c>
       <c r="M8" t="n">
-        <v>13.22587274246065</v>
+        <v>13.27799348024808</v>
       </c>
       <c r="N8" t="n">
-        <v>284.5740749720727</v>
+        <v>287.6928705585595</v>
       </c>
       <c r="O8" t="n">
-        <v>16.86932348886797</v>
+        <v>16.96151144675968</v>
       </c>
       <c r="P8" t="n">
-        <v>336.0412364360398</v>
+        <v>335.858451099978</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33981,28 +34051,28 @@
         <v>0.0566</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.36259149538277</v>
+        <v>-1.34654375442686</v>
       </c>
       <c r="J9" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K9" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3196160405521318</v>
+        <v>0.3125202584351278</v>
       </c>
       <c r="M9" t="n">
-        <v>11.6937848213847</v>
+        <v>11.74977142292601</v>
       </c>
       <c r="N9" t="n">
-        <v>224.9218385510254</v>
+        <v>227.5547431110078</v>
       </c>
       <c r="O9" t="n">
-        <v>14.99739439206109</v>
+        <v>15.0849177363023</v>
       </c>
       <c r="P9" t="n">
-        <v>332.2141255308069</v>
+        <v>332.0479711544855</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34059,28 +34129,28 @@
         <v>0.0488</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.224574431537746</v>
+        <v>-1.214830314437446</v>
       </c>
       <c r="J10" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K10" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2305117013228924</v>
+        <v>0.2278069486422153</v>
       </c>
       <c r="M10" t="n">
-        <v>13.38520378704193</v>
+        <v>13.40109102641782</v>
       </c>
       <c r="N10" t="n">
-        <v>282.642172738086</v>
+        <v>283.1668293585176</v>
       </c>
       <c r="O10" t="n">
-        <v>16.81196516585988</v>
+        <v>16.82756159871411</v>
       </c>
       <c r="P10" t="n">
-        <v>330.646492655515</v>
+        <v>330.5451061034387</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34137,28 +34207,28 @@
         <v>0.0619</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.371344599963771</v>
+        <v>-1.354918161101482</v>
       </c>
       <c r="J11" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K11" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2710113975708215</v>
+        <v>0.2649760912484866</v>
       </c>
       <c r="M11" t="n">
-        <v>12.96990412781817</v>
+        <v>13.02773397750431</v>
       </c>
       <c r="N11" t="n">
-        <v>287.2780217586287</v>
+        <v>289.9211740713279</v>
       </c>
       <c r="O11" t="n">
-        <v>16.94927791260232</v>
+        <v>17.02707179967618</v>
       </c>
       <c r="P11" t="n">
-        <v>327.0026592950122</v>
+        <v>326.8321223572743</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34215,28 +34285,28 @@
         <v>0.0561</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.004729858127691</v>
+        <v>-0.9884443154265201</v>
       </c>
       <c r="J12" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K12" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1448900365858844</v>
+        <v>0.1403093019097305</v>
       </c>
       <c r="M12" t="n">
-        <v>14.55352665046219</v>
+        <v>14.59752454192809</v>
       </c>
       <c r="N12" t="n">
-        <v>335.4982231664372</v>
+        <v>337.9438605818003</v>
       </c>
       <c r="O12" t="n">
-        <v>18.31661058073893</v>
+        <v>18.38324945655148</v>
       </c>
       <c r="P12" t="n">
-        <v>315.758021759462</v>
+        <v>315.5874569461952</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34293,28 +34363,28 @@
         <v>0.0425</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8993840111588729</v>
+        <v>-0.8834297370982865</v>
       </c>
       <c r="J13" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K13" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1326322654698178</v>
+        <v>0.1279465391299208</v>
       </c>
       <c r="M13" t="n">
-        <v>13.84797099726266</v>
+        <v>13.90786923197081</v>
       </c>
       <c r="N13" t="n">
-        <v>300.3397300379007</v>
+        <v>302.7680576494054</v>
       </c>
       <c r="O13" t="n">
-        <v>17.33031246221201</v>
+        <v>17.40023154010904</v>
       </c>
       <c r="P13" t="n">
-        <v>318.6853897938428</v>
+        <v>318.5197242336809</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34371,28 +34441,28 @@
         <v>0.0451</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.255335796369796</v>
+        <v>-1.239338503627847</v>
       </c>
       <c r="J14" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K14" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1912502128467836</v>
+        <v>0.186783963078431</v>
       </c>
       <c r="M14" t="n">
-        <v>15.3961467097826</v>
+        <v>15.44716602489996</v>
       </c>
       <c r="N14" t="n">
-        <v>378.0754164646009</v>
+        <v>380.3467860871072</v>
       </c>
       <c r="O14" t="n">
-        <v>19.44416150068192</v>
+        <v>19.50248153664316</v>
       </c>
       <c r="P14" t="n">
-        <v>322.3526184176844</v>
+        <v>322.186560020988</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34449,28 +34519,28 @@
         <v>0.0413</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.091452564577885</v>
+        <v>-1.07910801724294</v>
       </c>
       <c r="J15" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K15" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2112481683473598</v>
+        <v>0.207056470727412</v>
       </c>
       <c r="M15" t="n">
-        <v>12.48071734807879</v>
+        <v>12.52240263829535</v>
       </c>
       <c r="N15" t="n">
-        <v>251.8927572114081</v>
+        <v>253.1824338330536</v>
       </c>
       <c r="O15" t="n">
-        <v>15.87112967659858</v>
+        <v>15.91170744555887</v>
       </c>
       <c r="P15" t="n">
-        <v>315.6631244321037</v>
+        <v>315.5349272251406</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -34531,28 +34601,28 @@
         <v>0.0337</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6758988447249987</v>
+        <v>-0.6667474271343945</v>
       </c>
       <c r="J16" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K16" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1061185336775526</v>
+        <v>0.1035637350500109</v>
       </c>
       <c r="M16" t="n">
-        <v>11.59765703935564</v>
+        <v>11.62416073821634</v>
       </c>
       <c r="N16" t="n">
-        <v>218.2857665775336</v>
+        <v>218.8221530816702</v>
       </c>
       <c r="O16" t="n">
-        <v>14.77449716834836</v>
+        <v>14.79263847600117</v>
       </c>
       <c r="P16" t="n">
-        <v>306.1742992565582</v>
+        <v>306.0792121291263</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -34613,28 +34683,28 @@
         <v>0.1173</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2156447272339416</v>
+        <v>-0.2097826968203454</v>
       </c>
       <c r="J17" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K17" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01800967698975653</v>
+        <v>0.01709146245921389</v>
       </c>
       <c r="M17" t="n">
-        <v>7.895070898023206</v>
+        <v>7.902176460547047</v>
       </c>
       <c r="N17" t="n">
-        <v>141.445105312031</v>
+        <v>141.5412995368059</v>
       </c>
       <c r="O17" t="n">
-        <v>11.89306963369974</v>
+        <v>11.89711307573421</v>
       </c>
       <c r="P17" t="n">
-        <v>309.3701295487895</v>
+        <v>309.308578385924</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -34676,7 +34746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R461"/>
+  <dimension ref="A1:R462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76855,6 +76925,98 @@
         </is>
       </c>
     </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:42+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>-45.907446284794034,170.55145272160263</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>-45.90727670423174,170.55057946866725</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>-45.907242188933715,170.54968255988365</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>-45.90723257777378,170.54878332691237</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>-45.90717773318579,170.54788810538057</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>-45.907175133496665,170.5469893885372</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>-45.90721088901492,170.54609110400798</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>-45.90718068512834,170.5451954807077</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>-45.90703067299122,170.5443063127331</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>-45.90711169557186,170.54339937458258</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>-45.90711376087035,170.54250415033653</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>-45.90715031836058,170.5416069493291</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>-45.907094546310184,170.54070599505965</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>-45.90702613674935,170.5397968906411</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>-45.90702056576015,170.53887941930105</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>-45.907179797061275,170.53799469709315</t>
+        </is>
+      </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0510/nzd0510.xlsx
+++ b/data/nzd0510/nzd0510.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R462"/>
+  <dimension ref="A1:R463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28036,7 +28036,7 @@
         <v>333.97</v>
       </c>
       <c r="J462" t="n">
-        <v>321.07</v>
+        <v>329.59</v>
       </c>
       <c r="K462" t="n">
         <v>329.37</v>
@@ -28062,6 +28062,66 @@
       <c r="R462" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>340.44</v>
+      </c>
+      <c r="C463" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="D463" t="n">
+        <v>346.82</v>
+      </c>
+      <c r="E463" t="n">
+        <v>343.65</v>
+      </c>
+      <c r="F463" t="n">
+        <v>342.8</v>
+      </c>
+      <c r="G463" t="n">
+        <v>342.52</v>
+      </c>
+      <c r="H463" t="n">
+        <v>343.32</v>
+      </c>
+      <c r="I463" t="n">
+        <v>340.36</v>
+      </c>
+      <c r="J463" t="n">
+        <v>333.19</v>
+      </c>
+      <c r="K463" t="n">
+        <v>332.43</v>
+      </c>
+      <c r="L463" t="n">
+        <v>329.62</v>
+      </c>
+      <c r="M463" t="n">
+        <v>335.39</v>
+      </c>
+      <c r="N463" t="n">
+        <v>329.81</v>
+      </c>
+      <c r="O463" t="n">
+        <v>322.22</v>
+      </c>
+      <c r="P463" t="n">
+        <v>316.08</v>
+      </c>
+      <c r="Q463" t="n">
+        <v>314.86</v>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28076,7 +28136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B525"/>
+  <dimension ref="A1:B526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33329,6 +33389,16 @@
       </c>
       <c r="B525" t="n">
         <v>-0.93</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -33497,28 +33567,28 @@
         <v>0.1415</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7047760616464955</v>
+        <v>-0.6736474852094327</v>
       </c>
       <c r="J2" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K2" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03720867915652681</v>
+        <v>0.03373424240384004</v>
       </c>
       <c r="M2" t="n">
-        <v>22.24873272446845</v>
+        <v>22.38693348425319</v>
       </c>
       <c r="N2" t="n">
-        <v>727.2428892820952</v>
+        <v>737.3020775913362</v>
       </c>
       <c r="O2" t="n">
-        <v>26.96744128170293</v>
+        <v>27.1533069365655</v>
       </c>
       <c r="P2" t="n">
-        <v>286.6778376378032</v>
+        <v>286.3498563141501</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -33579,28 +33649,28 @@
         <v>0.119</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.672337598755424</v>
+        <v>-1.645183287708577</v>
       </c>
       <c r="J3" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K3" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1956634774380676</v>
+        <v>0.1892239147404745</v>
       </c>
       <c r="M3" t="n">
-        <v>19.85162093758423</v>
+        <v>19.90981500138246</v>
       </c>
       <c r="N3" t="n">
-        <v>653.9805377927016</v>
+        <v>661.3898963586141</v>
       </c>
       <c r="O3" t="n">
-        <v>25.57304318599375</v>
+        <v>25.7175017518929</v>
       </c>
       <c r="P3" t="n">
-        <v>330.7897166204515</v>
+        <v>330.5078467270905</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -33661,28 +33731,28 @@
         <v>0.0919</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.321966050264917</v>
+        <v>-1.303576942647587</v>
       </c>
       <c r="J4" t="n">
+        <v>462</v>
+      </c>
+      <c r="K4" t="n">
         <v>461</v>
       </c>
-      <c r="K4" t="n">
-        <v>460</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2324243735394671</v>
+        <v>0.2261175751659766</v>
       </c>
       <c r="M4" t="n">
-        <v>14.00376053225433</v>
+        <v>14.07366530590615</v>
       </c>
       <c r="N4" t="n">
-        <v>327.854528246378</v>
+        <v>331.2212505263573</v>
       </c>
       <c r="O4" t="n">
-        <v>18.10675366393374</v>
+        <v>18.19948489728095</v>
       </c>
       <c r="P4" t="n">
-        <v>338.522931184372</v>
+        <v>338.3316480536188</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33739,28 +33809,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.037052786129342</v>
+        <v>-1.021935299313188</v>
       </c>
       <c r="J5" t="n">
+        <v>462</v>
+      </c>
+      <c r="K5" t="n">
         <v>461</v>
       </c>
-      <c r="K5" t="n">
-        <v>460</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1816624748176764</v>
+        <v>0.1765690238765664</v>
       </c>
       <c r="M5" t="n">
-        <v>12.22203219263745</v>
+        <v>12.28171132574529</v>
       </c>
       <c r="N5" t="n">
-        <v>275.2136947815877</v>
+        <v>277.3726741316348</v>
       </c>
       <c r="O5" t="n">
-        <v>16.58956584065983</v>
+        <v>16.65450912310641</v>
       </c>
       <c r="P5" t="n">
-        <v>335.4983290854033</v>
+        <v>335.3410772889873</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33817,28 +33887,28 @@
         <v>0.0939</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9252670318748046</v>
+        <v>-0.9118060210759553</v>
       </c>
       <c r="J6" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1682499788117483</v>
+        <v>0.1636032085389965</v>
       </c>
       <c r="M6" t="n">
-        <v>11.31854105782268</v>
+        <v>11.36513846975814</v>
       </c>
       <c r="N6" t="n">
-        <v>237.0114114623676</v>
+        <v>238.6354073635583</v>
       </c>
       <c r="O6" t="n">
-        <v>15.39517494094717</v>
+        <v>15.44782856467401</v>
       </c>
       <c r="P6" t="n">
-        <v>335.9860051150126</v>
+        <v>335.8445126648354</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33895,28 +33965,28 @@
         <v>0.0557</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9363967110925796</v>
+        <v>-0.9220044386014025</v>
       </c>
       <c r="J7" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K7" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1906608749794406</v>
+        <v>0.184878658193441</v>
       </c>
       <c r="M7" t="n">
-        <v>10.99669149224231</v>
+        <v>11.04633909444795</v>
       </c>
       <c r="N7" t="n">
-        <v>208.1567404804983</v>
+        <v>210.1452252521637</v>
       </c>
       <c r="O7" t="n">
-        <v>14.42763807698607</v>
+        <v>14.49638662743802</v>
       </c>
       <c r="P7" t="n">
-        <v>333.8269615317453</v>
+        <v>333.6756580619393</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33973,28 +34043,28 @@
         <v>0.056</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.455828407047184</v>
+        <v>-1.43628468712155</v>
       </c>
       <c r="J8" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K8" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2947373575351261</v>
+        <v>0.2868606188155682</v>
       </c>
       <c r="M8" t="n">
-        <v>13.27799348024808</v>
+        <v>13.33952776918177</v>
       </c>
       <c r="N8" t="n">
-        <v>287.6928705585595</v>
+        <v>291.6652884250606</v>
       </c>
       <c r="O8" t="n">
-        <v>16.96151144675968</v>
+        <v>17.07821092576915</v>
       </c>
       <c r="P8" t="n">
-        <v>335.858451099978</v>
+        <v>335.6551212899519</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34051,28 +34121,28 @@
         <v>0.0566</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.34654375442686</v>
+        <v>-1.327885826841587</v>
       </c>
       <c r="J9" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K9" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3125202584351278</v>
+        <v>0.3036479593007692</v>
       </c>
       <c r="M9" t="n">
-        <v>11.74977142292601</v>
+        <v>11.81921566176633</v>
       </c>
       <c r="N9" t="n">
-        <v>227.5547431110078</v>
+        <v>231.2807023508791</v>
       </c>
       <c r="O9" t="n">
-        <v>15.0849177363023</v>
+        <v>15.20791577931963</v>
       </c>
       <c r="P9" t="n">
-        <v>332.0479711544855</v>
+        <v>331.8542218399757</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34129,28 +34199,28 @@
         <v>0.0488</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.214830314437446</v>
+        <v>-1.196402831291567</v>
       </c>
       <c r="J10" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K10" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2278069486422153</v>
+        <v>0.2210812848951319</v>
       </c>
       <c r="M10" t="n">
-        <v>13.40109102641782</v>
+        <v>13.4565809750391</v>
       </c>
       <c r="N10" t="n">
-        <v>283.1668293585176</v>
+        <v>286.1868852539418</v>
       </c>
       <c r="O10" t="n">
-        <v>16.82756159871411</v>
+        <v>16.91705900131408</v>
       </c>
       <c r="P10" t="n">
-        <v>330.5451061034387</v>
+        <v>330.3529195869357</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34207,28 +34277,28 @@
         <v>0.0619</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.354918161101482</v>
+        <v>-1.33728903161046</v>
       </c>
       <c r="J11" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K11" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2649760912484866</v>
+        <v>0.2583241186129935</v>
       </c>
       <c r="M11" t="n">
-        <v>13.02773397750431</v>
+        <v>13.09130120490142</v>
       </c>
       <c r="N11" t="n">
-        <v>289.9211740713279</v>
+        <v>293.0553464039055</v>
       </c>
       <c r="O11" t="n">
-        <v>17.02707179967618</v>
+        <v>17.11885937800488</v>
       </c>
       <c r="P11" t="n">
-        <v>326.8321223572743</v>
+        <v>326.648558907528</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34285,28 +34355,28 @@
         <v>0.0561</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9884443154265201</v>
+        <v>-0.9712220209417014</v>
       </c>
       <c r="J12" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K12" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1403093019097305</v>
+        <v>0.1354409163860825</v>
       </c>
       <c r="M12" t="n">
-        <v>14.59752454192809</v>
+        <v>14.64772453081014</v>
       </c>
       <c r="N12" t="n">
-        <v>337.9438605818003</v>
+        <v>340.7614297893993</v>
       </c>
       <c r="O12" t="n">
-        <v>18.38324945655148</v>
+        <v>18.45972453178539</v>
       </c>
       <c r="P12" t="n">
-        <v>315.5874569461952</v>
+        <v>315.4065490638455</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34363,28 +34433,28 @@
         <v>0.0425</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8834297370982865</v>
+        <v>-0.8663398250965502</v>
       </c>
       <c r="J13" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K13" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1279465391299208</v>
+        <v>0.1228992729000754</v>
       </c>
       <c r="M13" t="n">
-        <v>13.90786923197081</v>
+        <v>13.97407137637149</v>
       </c>
       <c r="N13" t="n">
-        <v>302.7680576494054</v>
+        <v>305.6462650291414</v>
       </c>
       <c r="O13" t="n">
-        <v>17.40023154010904</v>
+        <v>17.48274191965155</v>
       </c>
       <c r="P13" t="n">
-        <v>318.5197242336809</v>
+        <v>318.3417426605894</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34441,28 +34511,28 @@
         <v>0.0451</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.239338503627847</v>
+        <v>-1.222156252723558</v>
       </c>
       <c r="J14" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K14" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L14" t="n">
-        <v>0.186783963078431</v>
+        <v>0.1818846463092206</v>
       </c>
       <c r="M14" t="n">
-        <v>15.44716602489996</v>
+        <v>15.50381569987479</v>
       </c>
       <c r="N14" t="n">
-        <v>380.3467860871072</v>
+        <v>383.0896912954765</v>
       </c>
       <c r="O14" t="n">
-        <v>19.50248153664316</v>
+        <v>19.57267716219415</v>
       </c>
       <c r="P14" t="n">
-        <v>322.186560020988</v>
+        <v>322.007676304906</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34519,28 +34589,28 @@
         <v>0.0413</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.07910801724294</v>
+        <v>-1.064120818596123</v>
       </c>
       <c r="J15" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K15" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L15" t="n">
-        <v>0.207056470727412</v>
+        <v>0.2015410750548094</v>
       </c>
       <c r="M15" t="n">
-        <v>12.52240263829535</v>
+        <v>12.57857687530846</v>
       </c>
       <c r="N15" t="n">
-        <v>253.1824338330536</v>
+        <v>255.3411059342317</v>
       </c>
       <c r="O15" t="n">
-        <v>15.91170744555887</v>
+        <v>15.97939629442338</v>
       </c>
       <c r="P15" t="n">
-        <v>315.5349272251406</v>
+        <v>315.3788299380252</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -34601,28 +34671,28 @@
         <v>0.0337</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6667474271343945</v>
+        <v>-0.654998225440685</v>
       </c>
       <c r="J16" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K16" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1035637350500109</v>
+        <v>0.1000452271509061</v>
       </c>
       <c r="M16" t="n">
-        <v>11.62416073821634</v>
+        <v>11.66608921109004</v>
       </c>
       <c r="N16" t="n">
-        <v>218.8221530816702</v>
+        <v>220.0152807085567</v>
       </c>
       <c r="O16" t="n">
-        <v>14.79263847600117</v>
+        <v>14.83291207782736</v>
       </c>
       <c r="P16" t="n">
-        <v>306.0792121291263</v>
+        <v>305.9567728912756</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -34683,28 +34753,28 @@
         <v>0.1173</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2097826968203454</v>
+        <v>-0.2050095234899725</v>
       </c>
       <c r="J17" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K17" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01709146245921389</v>
+        <v>0.01638075766716729</v>
       </c>
       <c r="M17" t="n">
-        <v>7.902176460547047</v>
+        <v>7.905039607142288</v>
       </c>
       <c r="N17" t="n">
-        <v>141.5412995368059</v>
+        <v>141.5011618403024</v>
       </c>
       <c r="O17" t="n">
-        <v>11.89711307573421</v>
+        <v>11.89542608906055</v>
       </c>
       <c r="P17" t="n">
-        <v>309.308578385924</v>
+        <v>309.2583151752826</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -34746,7 +34816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R462"/>
+  <dimension ref="A1:R463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76973,7 +77043,7 @@
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>-45.90703067299122,170.5443063127331</t>
+          <t>-45.90710725065313,170.5443015440076</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
@@ -77014,6 +77084,98 @@
       <c r="R462" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>-45.907362321749446,170.55146919615933</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>-45.90737781449341,170.55056433879923</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>-45.907316671232216,170.549674962162</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>-45.907257625566466,170.5487810043858</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>-45.90722656049118,170.54788592909233</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>-45.90723549962961,170.54698912117536</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>-45.907253891997534,170.5460909130723</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>-45.90723812814928,170.54519224161447</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>-45.90713960741125,170.5442995290479</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>-45.907139224759895,170.5433994264253</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>-45.90713562065876,170.54250376706116</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>-45.907176573183136,170.54160568355013</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>-45.90712171561755,170.54070594910297</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>-45.90708366685079,170.5398002317107</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>-45.90707665476059,170.5388866844703</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>-45.90715793086452,170.5379907249361</t>
+        </is>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0510/nzd0510.xlsx
+++ b/data/nzd0510/nzd0510.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R463"/>
+  <dimension ref="A1:R469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28122,6 +28122,366 @@
       <c r="R463" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>324.55</v>
+      </c>
+      <c r="C464" t="n">
+        <v>345.81</v>
+      </c>
+      <c r="D464" t="n">
+        <v>345.19</v>
+      </c>
+      <c r="E464" t="n">
+        <v>342.84</v>
+      </c>
+      <c r="F464" t="n">
+        <v>343.35</v>
+      </c>
+      <c r="G464" t="n">
+        <v>343.12</v>
+      </c>
+      <c r="H464" t="n">
+        <v>343.55</v>
+      </c>
+      <c r="I464" t="n">
+        <v>340.27</v>
+      </c>
+      <c r="J464" t="n">
+        <v>334.29</v>
+      </c>
+      <c r="K464" t="n">
+        <v>332.31</v>
+      </c>
+      <c r="L464" t="n">
+        <v>329.67</v>
+      </c>
+      <c r="M464" t="n">
+        <v>335.29</v>
+      </c>
+      <c r="N464" t="n">
+        <v>328.12</v>
+      </c>
+      <c r="O464" t="n">
+        <v>321.12</v>
+      </c>
+      <c r="P464" t="n">
+        <v>315.41</v>
+      </c>
+      <c r="Q464" t="n">
+        <v>313.17</v>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>313.14</v>
+      </c>
+      <c r="C465" t="n">
+        <v>343.1</v>
+      </c>
+      <c r="D465" t="n">
+        <v>342.99</v>
+      </c>
+      <c r="E465" t="n">
+        <v>340.51</v>
+      </c>
+      <c r="F465" t="n">
+        <v>341.53</v>
+      </c>
+      <c r="G465" t="n">
+        <v>341.68</v>
+      </c>
+      <c r="H465" t="n">
+        <v>341.96</v>
+      </c>
+      <c r="I465" t="n">
+        <v>338.77</v>
+      </c>
+      <c r="J465" t="n">
+        <v>333.72</v>
+      </c>
+      <c r="K465" t="n">
+        <v>330.75</v>
+      </c>
+      <c r="L465" t="n">
+        <v>328.35</v>
+      </c>
+      <c r="M465" t="n">
+        <v>334.58</v>
+      </c>
+      <c r="N465" t="n">
+        <v>326.67</v>
+      </c>
+      <c r="O465" t="n">
+        <v>317.92</v>
+      </c>
+      <c r="P465" t="n">
+        <v>312.2</v>
+      </c>
+      <c r="Q465" t="n">
+        <v>310.95</v>
+      </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>303.08</v>
+      </c>
+      <c r="C466" t="n">
+        <v>341.27</v>
+      </c>
+      <c r="D466" t="n">
+        <v>341.67</v>
+      </c>
+      <c r="E466" t="n">
+        <v>338.99</v>
+      </c>
+      <c r="F466" t="n">
+        <v>340.8</v>
+      </c>
+      <c r="G466" t="n">
+        <v>340.72</v>
+      </c>
+      <c r="H466" t="n">
+        <v>342.09</v>
+      </c>
+      <c r="I466" t="n">
+        <v>338.32</v>
+      </c>
+      <c r="J466" t="n">
+        <v>333.61</v>
+      </c>
+      <c r="K466" t="n">
+        <v>330.22</v>
+      </c>
+      <c r="L466" t="n">
+        <v>328.35</v>
+      </c>
+      <c r="M466" t="n">
+        <v>333.89</v>
+      </c>
+      <c r="N466" t="n">
+        <v>326.19</v>
+      </c>
+      <c r="O466" t="n">
+        <v>316.17</v>
+      </c>
+      <c r="P466" t="n">
+        <v>310.92</v>
+      </c>
+      <c r="Q466" t="n">
+        <v>310.91</v>
+      </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>296.34</v>
+      </c>
+      <c r="C467" t="n">
+        <v>339.13</v>
+      </c>
+      <c r="D467" t="n">
+        <v>340.61</v>
+      </c>
+      <c r="E467" t="n">
+        <v>337.07</v>
+      </c>
+      <c r="F467" t="n">
+        <v>338.8</v>
+      </c>
+      <c r="G467" t="n">
+        <v>338.84</v>
+      </c>
+      <c r="H467" t="n">
+        <v>339.8</v>
+      </c>
+      <c r="I467" t="n">
+        <v>336.17</v>
+      </c>
+      <c r="J467" t="n">
+        <v>332.12</v>
+      </c>
+      <c r="K467" t="n">
+        <v>328.51</v>
+      </c>
+      <c r="L467" t="n">
+        <v>326.61</v>
+      </c>
+      <c r="M467" t="n">
+        <v>331.62</v>
+      </c>
+      <c r="N467" t="n">
+        <v>324.79</v>
+      </c>
+      <c r="O467" t="n">
+        <v>313.35</v>
+      </c>
+      <c r="P467" t="n">
+        <v>309.72</v>
+      </c>
+      <c r="Q467" t="n">
+        <v>309.16</v>
+      </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>296.34</v>
+      </c>
+      <c r="C468" t="n">
+        <v>337.96</v>
+      </c>
+      <c r="D468" t="n">
+        <v>340.77</v>
+      </c>
+      <c r="E468" t="n">
+        <v>337.33</v>
+      </c>
+      <c r="F468" t="n">
+        <v>339.39</v>
+      </c>
+      <c r="G468" t="n">
+        <v>338.82</v>
+      </c>
+      <c r="H468" t="n">
+        <v>340.31</v>
+      </c>
+      <c r="I468" t="n">
+        <v>336.59</v>
+      </c>
+      <c r="J468" t="n">
+        <v>333.06</v>
+      </c>
+      <c r="K468" t="n">
+        <v>329.78</v>
+      </c>
+      <c r="L468" t="n">
+        <v>327.09</v>
+      </c>
+      <c r="M468" t="n">
+        <v>330.86</v>
+      </c>
+      <c r="N468" t="n">
+        <v>324.42</v>
+      </c>
+      <c r="O468" t="n">
+        <v>312.51</v>
+      </c>
+      <c r="P468" t="n">
+        <v>309.83</v>
+      </c>
+      <c r="Q468" t="n">
+        <v>309.76</v>
+      </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>296.34</v>
+      </c>
+      <c r="C469" t="n">
+        <v>338.65</v>
+      </c>
+      <c r="D469" t="n">
+        <v>341.85</v>
+      </c>
+      <c r="E469" t="n">
+        <v>339.25</v>
+      </c>
+      <c r="F469" t="n">
+        <v>341.98</v>
+      </c>
+      <c r="G469" t="n">
+        <v>340.72</v>
+      </c>
+      <c r="H469" t="n">
+        <v>341.87</v>
+      </c>
+      <c r="I469" t="n">
+        <v>337.84</v>
+      </c>
+      <c r="J469" t="n">
+        <v>334.66</v>
+      </c>
+      <c r="K469" t="n">
+        <v>332.14</v>
+      </c>
+      <c r="L469" t="n">
+        <v>327.82</v>
+      </c>
+      <c r="M469" t="n">
+        <v>330.59</v>
+      </c>
+      <c r="N469" t="n">
+        <v>324.15</v>
+      </c>
+      <c r="O469" t="n">
+        <v>312.5</v>
+      </c>
+      <c r="P469" t="n">
+        <v>309.79</v>
+      </c>
+      <c r="Q469" t="n">
+        <v>310.78</v>
+      </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28136,7 +28496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B526"/>
+  <dimension ref="A1:B532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33399,6 +33759,66 @@
       </c>
       <c r="B526" t="n">
         <v>0.3</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -33567,28 +33987,28 @@
         <v>0.1415</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6736474852094327</v>
+        <v>-0.5827337227199647</v>
       </c>
       <c r="J2" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="K2" t="n">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03373424240384004</v>
+        <v>0.02552010824868767</v>
       </c>
       <c r="M2" t="n">
-        <v>22.38693348425319</v>
+        <v>22.63187624325821</v>
       </c>
       <c r="N2" t="n">
-        <v>737.3020775913362</v>
+        <v>746.0552088801885</v>
       </c>
       <c r="O2" t="n">
-        <v>27.1533069365655</v>
+        <v>27.31401121915616</v>
       </c>
       <c r="P2" t="n">
-        <v>286.3498563141501</v>
+        <v>285.3896296160513</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -33649,28 +34069,28 @@
         <v>0.119</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.645183287708577</v>
+        <v>-1.511347175699131</v>
       </c>
       <c r="J3" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="K3" t="n">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1892239147404745</v>
+        <v>0.1608923102953672</v>
       </c>
       <c r="M3" t="n">
-        <v>19.90981500138246</v>
+        <v>20.17760875122705</v>
       </c>
       <c r="N3" t="n">
-        <v>661.3898963586141</v>
+        <v>689.5967313477485</v>
       </c>
       <c r="O3" t="n">
-        <v>25.7175017518929</v>
+        <v>26.26017386362376</v>
       </c>
       <c r="P3" t="n">
-        <v>330.5078467270905</v>
+        <v>329.114965246562</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -33731,28 +34151,28 @@
         <v>0.0919</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.303576942647587</v>
+        <v>-1.208978967758916</v>
       </c>
       <c r="J4" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="K4" t="n">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2261175751659766</v>
+        <v>0.1965123671532811</v>
       </c>
       <c r="M4" t="n">
-        <v>14.07366530590615</v>
+        <v>14.41208716858679</v>
       </c>
       <c r="N4" t="n">
-        <v>331.2212505263573</v>
+        <v>345.4164949000378</v>
       </c>
       <c r="O4" t="n">
-        <v>18.19948489728095</v>
+        <v>18.58538390510236</v>
       </c>
       <c r="P4" t="n">
-        <v>338.3316480536188</v>
+        <v>337.3450540047846</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33809,28 +34229,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.021935299313188</v>
+        <v>-0.9453895175240745</v>
       </c>
       <c r="J5" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="K5" t="n">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1765690238765664</v>
+        <v>0.1530258930979186</v>
       </c>
       <c r="M5" t="n">
-        <v>12.28171132574529</v>
+        <v>12.56264668384289</v>
       </c>
       <c r="N5" t="n">
-        <v>277.3726741316348</v>
+        <v>285.9190209143101</v>
       </c>
       <c r="O5" t="n">
-        <v>16.65450912310641</v>
+        <v>16.90914015892914</v>
       </c>
       <c r="P5" t="n">
-        <v>335.3410772889873</v>
+        <v>334.5427700198759</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33887,28 +34307,28 @@
         <v>0.0939</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9118060210759553</v>
+        <v>-0.838773314548372</v>
       </c>
       <c r="J6" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="K6" t="n">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1636032085389965</v>
+        <v>0.1399705633678167</v>
       </c>
       <c r="M6" t="n">
-        <v>11.36513846975814</v>
+        <v>11.62618946750258</v>
       </c>
       <c r="N6" t="n">
-        <v>238.6354073635583</v>
+        <v>246.3423580343925</v>
       </c>
       <c r="O6" t="n">
-        <v>15.44782856467401</v>
+        <v>15.69529732226798</v>
       </c>
       <c r="P6" t="n">
-        <v>335.8445126648354</v>
+        <v>335.0748496465068</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33965,28 +34385,28 @@
         <v>0.0557</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9220044386014025</v>
+        <v>-0.8437224697397904</v>
       </c>
       <c r="J7" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="K7" t="n">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="L7" t="n">
-        <v>0.184878658193441</v>
+        <v>0.1556363630453357</v>
       </c>
       <c r="M7" t="n">
-        <v>11.04633909444795</v>
+        <v>11.30119970413506</v>
       </c>
       <c r="N7" t="n">
-        <v>210.1452252521637</v>
+        <v>219.7980361718857</v>
       </c>
       <c r="O7" t="n">
-        <v>14.49638662743802</v>
+        <v>14.8255872117055</v>
       </c>
       <c r="P7" t="n">
-        <v>333.6756580619393</v>
+        <v>332.8505681689468</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34043,28 +34463,28 @@
         <v>0.056</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.43628468712155</v>
+        <v>-1.327872371362874</v>
       </c>
       <c r="J8" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="K8" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2868606188155682</v>
+        <v>0.2459226053112592</v>
       </c>
       <c r="M8" t="n">
-        <v>13.33952776918177</v>
+        <v>13.67120122226583</v>
       </c>
       <c r="N8" t="n">
-        <v>291.6652884250606</v>
+        <v>312.0803486128235</v>
       </c>
       <c r="O8" t="n">
-        <v>17.07821092576915</v>
+        <v>17.66579600846855</v>
       </c>
       <c r="P8" t="n">
-        <v>335.6551212899519</v>
+        <v>334.5242453210121</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34121,28 +34541,28 @@
         <v>0.0566</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.327885826841587</v>
+        <v>-1.226156166836202</v>
       </c>
       <c r="J9" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="K9" t="n">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3036479593007692</v>
+        <v>0.2589337676978566</v>
       </c>
       <c r="M9" t="n">
-        <v>11.81921566176633</v>
+        <v>12.19694445328458</v>
       </c>
       <c r="N9" t="n">
-        <v>231.2807023508791</v>
+        <v>249.7412932798501</v>
       </c>
       <c r="O9" t="n">
-        <v>15.20791577931963</v>
+        <v>15.80320515844334</v>
       </c>
       <c r="P9" t="n">
-        <v>331.8542218399757</v>
+        <v>330.7950266148394</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34199,28 +34619,28 @@
         <v>0.0488</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.196402831291567</v>
+        <v>-1.110053764585911</v>
       </c>
       <c r="J10" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="K10" t="n">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2210812848951319</v>
+        <v>0.1924463958397288</v>
       </c>
       <c r="M10" t="n">
-        <v>13.4565809750391</v>
+        <v>13.68400365252123</v>
       </c>
       <c r="N10" t="n">
-        <v>286.1868852539418</v>
+        <v>297.7916224876739</v>
       </c>
       <c r="O10" t="n">
-        <v>16.91705900131408</v>
+        <v>17.25663995358522</v>
       </c>
       <c r="P10" t="n">
-        <v>330.3529195869357</v>
+        <v>329.4494483776281</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34277,28 +34697,28 @@
         <v>0.0619</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.33728903161046</v>
+        <v>-1.240113574510566</v>
       </c>
       <c r="J11" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="K11" t="n">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2583241186129935</v>
+        <v>0.223846914630726</v>
       </c>
       <c r="M11" t="n">
-        <v>13.09130120490142</v>
+        <v>13.42827757933266</v>
       </c>
       <c r="N11" t="n">
-        <v>293.0553464039055</v>
+        <v>308.8223962230987</v>
       </c>
       <c r="O11" t="n">
-        <v>17.11885937800488</v>
+        <v>17.57334334220722</v>
       </c>
       <c r="P11" t="n">
-        <v>326.648558907528</v>
+        <v>325.6340099078658</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34355,28 +34775,28 @@
         <v>0.0561</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9712220209417014</v>
+        <v>-0.876057443023896</v>
       </c>
       <c r="J12" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="K12" t="n">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1354409163860825</v>
+        <v>0.110460245840815</v>
       </c>
       <c r="M12" t="n">
-        <v>14.64772453081014</v>
+        <v>14.92228250683766</v>
       </c>
       <c r="N12" t="n">
-        <v>340.7614297893993</v>
+        <v>354.8892631462097</v>
       </c>
       <c r="O12" t="n">
-        <v>18.45972453178539</v>
+        <v>18.83850480123647</v>
       </c>
       <c r="P12" t="n">
-        <v>315.4065490638455</v>
+        <v>314.4042520460629</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34433,28 +34853,28 @@
         <v>0.0425</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8663398250965502</v>
+        <v>-0.7742533363435173</v>
       </c>
       <c r="J13" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="K13" t="n">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1228992729000754</v>
+        <v>0.09805310834043302</v>
       </c>
       <c r="M13" t="n">
-        <v>13.97407137637149</v>
+        <v>14.32076614513651</v>
       </c>
       <c r="N13" t="n">
-        <v>305.6462650291414</v>
+        <v>319.2774447223882</v>
       </c>
       <c r="O13" t="n">
-        <v>17.48274191965155</v>
+        <v>17.86833637254426</v>
       </c>
       <c r="P13" t="n">
-        <v>318.3417426605894</v>
+        <v>317.3801903665376</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34511,28 +34931,28 @@
         <v>0.0451</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.222156252723558</v>
+        <v>-1.133154380695106</v>
       </c>
       <c r="J14" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="K14" t="n">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1818846463092206</v>
+        <v>0.1584747733916254</v>
       </c>
       <c r="M14" t="n">
-        <v>15.50381569987479</v>
+        <v>15.7869750678436</v>
       </c>
       <c r="N14" t="n">
-        <v>383.0896912954765</v>
+        <v>394.5279016911032</v>
       </c>
       <c r="O14" t="n">
-        <v>19.57267716219415</v>
+        <v>19.86272644153122</v>
       </c>
       <c r="P14" t="n">
-        <v>322.007676304906</v>
+        <v>321.0786379225895</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34589,28 +35009,28 @@
         <v>0.0413</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.064120818596123</v>
+        <v>-0.9940024539631798</v>
       </c>
       <c r="J15" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="K15" t="n">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2015410750548094</v>
+        <v>0.178694911116173</v>
       </c>
       <c r="M15" t="n">
-        <v>12.57857687530846</v>
+        <v>12.80727442269871</v>
       </c>
       <c r="N15" t="n">
-        <v>255.3411059342317</v>
+        <v>262.3060107424039</v>
       </c>
       <c r="O15" t="n">
-        <v>15.97939629442338</v>
+        <v>16.19586400110855</v>
       </c>
       <c r="P15" t="n">
-        <v>315.3788299380252</v>
+        <v>314.6466574967795</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -34671,28 +35091,28 @@
         <v>0.0337</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.654998225440685</v>
+        <v>-0.5990198476711425</v>
       </c>
       <c r="J16" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="K16" t="n">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1000452271509061</v>
+        <v>0.08491300977384575</v>
       </c>
       <c r="M16" t="n">
-        <v>11.66608921109004</v>
+        <v>11.83630327651375</v>
       </c>
       <c r="N16" t="n">
-        <v>220.0152807085567</v>
+        <v>223.6978677515252</v>
       </c>
       <c r="O16" t="n">
-        <v>14.83291207782736</v>
+        <v>14.9565326112547</v>
       </c>
       <c r="P16" t="n">
-        <v>305.9567728912756</v>
+        <v>305.3719026336535</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -34753,28 +35173,28 @@
         <v>0.1173</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2050095234899725</v>
+        <v>-0.1876308900110672</v>
       </c>
       <c r="J17" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="K17" t="n">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01638075766716729</v>
+        <v>0.01407848416980517</v>
       </c>
       <c r="M17" t="n">
-        <v>7.905039607142288</v>
+        <v>7.877470805316316</v>
       </c>
       <c r="N17" t="n">
-        <v>141.5011618403024</v>
+        <v>140.3003915967062</v>
       </c>
       <c r="O17" t="n">
-        <v>11.89542608906055</v>
+        <v>11.84484662613688</v>
       </c>
       <c r="P17" t="n">
-        <v>309.2583151752826</v>
+        <v>309.0748558667139</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -34816,7 +35236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R463"/>
+  <dimension ref="A1:R469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77179,6 +77599,558 @@
         </is>
       </c>
     </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>-45.907220689809485,170.5514969859189</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>-45.907338980995256,170.5505701497471</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>-45.907302043985794,170.5496764542466</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>-45.907250353626665,170.54878167866798</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>-45.907231506166646,170.54788570865767</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>-45.90724089749542,170.546989097268</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>-45.9072559611787,170.546090903885</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>-45.907237319092644,170.54519228723555</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>-45.90714949419841,170.54429891336517</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>-45.907138145183886,170.54339942439228</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>-45.90713607044865,170.54250375917485</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>-45.907175674045384,170.54160572689875</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>-45.907106511601185,170.54070597482053</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>-45.90707377886464,170.53979965746404</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>-45.9070706516248,170.5388859068877</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>-45.90714284765117,170.53798798495995</t>
+        </is>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>-45.90711898933367,170.5515169405839</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>-45.90731473242807,170.55057377823752</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>-45.90728230168989,170.54967846810166</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>-45.90722943557755,170.54878361826857</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>-45.90721514047688,170.5478864380958</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>-45.90722794261747,170.54698915464556</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>-45.90724165683933,170.54609096739728</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>-45.907223834815504,170.54519304758688</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>-45.907144371045064,170.5442992324008</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>-45.90712411069589,170.5433993979627</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>-45.90712419599569,170.5425039673739</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>-45.9071692901673,170.54160603467395</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>-45.90709346673504,170.54070599688572</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>-45.90704501381395,170.53979798692905</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>-45.90704189033228,170.5388821814566</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>-45.9071230341992,170.5379843857034</t>
+        </is>
+      </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>-45.90702932177458,170.55153453420073</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>-45.907298357934195,170.55057622847067</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>-45.90727045631228,170.54967967641383</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>-45.90721578946819,170.54878488358645</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>-45.90720857621669,170.54788673067245</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>-45.90721930603216,170.54698919289717</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>-45.90724282637651,170.54609096220443</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>-45.90721978953235,170.54519327569216</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>-45.90714338236635,170.5442992939691</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>-45.90711934256854,170.5433993889834</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>-45.90712419599569,170.5425039673739</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>-45.90716308611677,170.54160633377927</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>-45.90708914843452,170.54070600419007</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>-45.90702928292678,170.53979707335571</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>-45.90703042165484,170.53888069592733</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>-45.907122677200064,170.53798432085193</t>
+        </is>
+      </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>-45.90696924628976,170.55154632153923</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>-45.90727920961882,170.55057909376862</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>-45.90726094411507,170.5496806467247</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>-45.907198552277315,170.54878648188165</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>-45.90719059194214,170.5478875322518</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>-45.90720239271921,170.5469892678064</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>-45.90722222452921,170.54609105367783</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>-45.90720046206834,170.54519436552795</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>-45.90712999026373,170.54430012793904</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>-45.9071039586105,170.5433993600123</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>-45.90710854330769,170.5425042418178</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>-45.90714267568959,170.54160731779183</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>-45.907076553391335,170.5407060254942</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>-45.9070039337257,170.53979560119822</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>-45.90701966976971,170.5388793032441</t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>-45.907107058487824,170.53798148360178</t>
+        </is>
+      </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>-45.90696924628976,170.55154632153923</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>-45.90726874067998,170.55058066030907</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>-45.90726237991843,170.54968050026272</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>-45.907200886480254,170.54878626544593</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>-45.90719589730315,170.54788729578598</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>-45.90720221279035,170.54698926860328</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>-45.907226812713546,170.54609103330606</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>-45.907204237665965,170.54519415262988</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>-45.90713843897277,170.5442996018104</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>-45.907115384123195,170.54339938152887</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>-45.9071128612906,170.54250416610915</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>-45.90713584224259,170.54160764724074</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>-45.907073224701335,170.54070603112459</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>-45.90699638289982,170.5397951626834</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>-45.90702065535919,170.53887943090675</t>
+        </is>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>-45.907112413474884,170.5379824563731</t>
+        </is>
+      </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>-45.90696924628976,170.55154632153923</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>-45.907274914669564,170.55057973645197</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>-45.90727207159105,170.54967951164403</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>-45.90721812367111,170.54878466715056</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>-45.90721918693864,170.5478862577403</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>-45.90721930603216,170.54698919289717</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>-45.907240847159756,170.54609097099228</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>-45.90721547456364,170.54519351900444</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>-45.90715281975408,170.5442987062718</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>-45.90713661578455,170.54339942151216</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>-45.90711942822292,170.54250405096892</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>-45.90713341457064,170.54160776428176</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>-45.90707079565729,170.5407060352332</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>-45.90699629300903,170.53979515746298</t>
+        </is>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>-45.907020296963026,170.53887938448398</t>
+        </is>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>-45.90712151695287,170.53798411008475</t>
+        </is>
+      </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0510/nzd0510.xlsx
+++ b/data/nzd0510/nzd0510.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R469"/>
+  <dimension ref="A1:R472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28480,6 +28480,186 @@
         <v>310.78</v>
       </c>
       <c r="R469" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>290.05</v>
+      </c>
+      <c r="C470" t="n">
+        <v>338.65</v>
+      </c>
+      <c r="D470" t="n">
+        <v>341.85</v>
+      </c>
+      <c r="E470" t="n">
+        <v>339.25</v>
+      </c>
+      <c r="F470" t="n">
+        <v>341.98</v>
+      </c>
+      <c r="G470" t="n">
+        <v>340.72</v>
+      </c>
+      <c r="H470" t="n">
+        <v>341.87</v>
+      </c>
+      <c r="I470" t="n">
+        <v>337.84</v>
+      </c>
+      <c r="J470" t="n">
+        <v>334.66</v>
+      </c>
+      <c r="K470" t="n">
+        <v>324.09</v>
+      </c>
+      <c r="L470" t="n">
+        <v>320.27</v>
+      </c>
+      <c r="M470" t="n">
+        <v>323.65</v>
+      </c>
+      <c r="N470" t="n">
+        <v>324.15</v>
+      </c>
+      <c r="O470" t="n">
+        <v>312.5</v>
+      </c>
+      <c r="P470" t="n">
+        <v>309.79</v>
+      </c>
+      <c r="Q470" t="n">
+        <v>310.78</v>
+      </c>
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>283.3</v>
+      </c>
+      <c r="C471" t="n">
+        <v>335.43</v>
+      </c>
+      <c r="D471" t="n">
+        <v>342.17</v>
+      </c>
+      <c r="E471" t="n">
+        <v>340.57</v>
+      </c>
+      <c r="F471" t="n">
+        <v>343.09</v>
+      </c>
+      <c r="G471" t="n">
+        <v>340.15</v>
+      </c>
+      <c r="H471" t="n">
+        <v>341.15</v>
+      </c>
+      <c r="I471" t="n">
+        <v>336.28</v>
+      </c>
+      <c r="J471" t="n">
+        <v>332.98</v>
+      </c>
+      <c r="K471" t="n">
+        <v>319.35</v>
+      </c>
+      <c r="L471" t="n">
+        <v>309.79</v>
+      </c>
+      <c r="M471" t="n">
+        <v>319.19</v>
+      </c>
+      <c r="N471" t="n">
+        <v>322.83</v>
+      </c>
+      <c r="O471" t="n">
+        <v>311.76</v>
+      </c>
+      <c r="P471" t="n">
+        <v>310.12</v>
+      </c>
+      <c r="Q471" t="n">
+        <v>310.87</v>
+      </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>283.3</v>
+      </c>
+      <c r="C472" t="n">
+        <v>335.43</v>
+      </c>
+      <c r="D472" t="n">
+        <v>340.64</v>
+      </c>
+      <c r="E472" t="n">
+        <v>339.23</v>
+      </c>
+      <c r="F472" t="n">
+        <v>341.94</v>
+      </c>
+      <c r="G472" t="n">
+        <v>338.72</v>
+      </c>
+      <c r="H472" t="n">
+        <v>338.99</v>
+      </c>
+      <c r="I472" t="n">
+        <v>334.16</v>
+      </c>
+      <c r="J472" t="n">
+        <v>330.01</v>
+      </c>
+      <c r="K472" t="n">
+        <v>319.35</v>
+      </c>
+      <c r="L472" t="n">
+        <v>301.79</v>
+      </c>
+      <c r="M472" t="n">
+        <v>319.19</v>
+      </c>
+      <c r="N472" t="n">
+        <v>322.83</v>
+      </c>
+      <c r="O472" t="n">
+        <v>308.25</v>
+      </c>
+      <c r="P472" t="n">
+        <v>306.98</v>
+      </c>
+      <c r="Q472" t="n">
+        <v>310.3</v>
+      </c>
+      <c r="R472" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28496,7 +28676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B532"/>
+  <dimension ref="A1:B535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33819,6 +33999,36 @@
       </c>
       <c r="B532" t="n">
         <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>-0.78</v>
       </c>
     </row>
   </sheetData>
@@ -33987,28 +34197,28 @@
         <v>0.1415</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5827337227199647</v>
+        <v>-0.5633236406293148</v>
       </c>
       <c r="J2" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K2" t="n">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02552010824868767</v>
+        <v>0.02415215892586453</v>
       </c>
       <c r="M2" t="n">
-        <v>22.63187624325821</v>
+        <v>22.60377916315513</v>
       </c>
       <c r="N2" t="n">
-        <v>746.0552088801885</v>
+        <v>742.8187387012679</v>
       </c>
       <c r="O2" t="n">
-        <v>27.31401121915616</v>
+        <v>27.2547012220143</v>
       </c>
       <c r="P2" t="n">
-        <v>285.3896296160513</v>
+        <v>285.1835527499109</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -34069,28 +34279,28 @@
         <v>0.119</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.511347175699131</v>
+        <v>-1.453021565677021</v>
       </c>
       <c r="J3" t="n">
+        <v>471</v>
+      </c>
+      <c r="K3" t="n">
         <v>468</v>
       </c>
-      <c r="K3" t="n">
-        <v>465</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1608923102953672</v>
+        <v>0.1496327800221228</v>
       </c>
       <c r="M3" t="n">
-        <v>20.17760875122705</v>
+        <v>20.28861863227469</v>
       </c>
       <c r="N3" t="n">
-        <v>689.5967313477485</v>
+        <v>699.6034266342986</v>
       </c>
       <c r="O3" t="n">
-        <v>26.26017386362376</v>
+        <v>26.45001751671062</v>
       </c>
       <c r="P3" t="n">
-        <v>329.114965246562</v>
+        <v>328.5049479602397</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -34151,28 +34361,28 @@
         <v>0.0919</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.208978967758916</v>
+        <v>-1.164616621396653</v>
       </c>
       <c r="J4" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K4" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1965123671532811</v>
+        <v>0.1833844211181913</v>
       </c>
       <c r="M4" t="n">
-        <v>14.41208716858679</v>
+        <v>14.57067473020613</v>
       </c>
       <c r="N4" t="n">
-        <v>345.4164949000378</v>
+        <v>351.6005298847131</v>
       </c>
       <c r="O4" t="n">
-        <v>18.58538390510236</v>
+        <v>18.75101410283489</v>
       </c>
       <c r="P4" t="n">
-        <v>337.3450540047846</v>
+        <v>336.8800971662593</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34229,28 +34439,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9453895175240745</v>
+        <v>-0.9084592382310985</v>
       </c>
       <c r="J5" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K5" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1530258930979186</v>
+        <v>0.1421622330029833</v>
       </c>
       <c r="M5" t="n">
-        <v>12.56264668384289</v>
+        <v>12.70537850213112</v>
       </c>
       <c r="N5" t="n">
-        <v>285.9190209143101</v>
+        <v>289.9079653438549</v>
       </c>
       <c r="O5" t="n">
-        <v>16.90914015892914</v>
+        <v>17.02668392094758</v>
       </c>
       <c r="P5" t="n">
-        <v>334.5427700198759</v>
+        <v>334.1557048148842</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34307,28 +34517,28 @@
         <v>0.0939</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.838773314548372</v>
+        <v>-0.8022890118532284</v>
       </c>
       <c r="J6" t="n">
+        <v>471</v>
+      </c>
+      <c r="K6" t="n">
         <v>468</v>
       </c>
-      <c r="K6" t="n">
-        <v>465</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1399705633678167</v>
+        <v>0.1286123875632355</v>
       </c>
       <c r="M6" t="n">
-        <v>11.62618946750258</v>
+        <v>11.76335477461417</v>
       </c>
       <c r="N6" t="n">
-        <v>246.3423580343925</v>
+        <v>250.3227992260232</v>
       </c>
       <c r="O6" t="n">
-        <v>15.69529732226798</v>
+        <v>15.82159281570674</v>
       </c>
       <c r="P6" t="n">
-        <v>335.0748496465068</v>
+        <v>334.6884769213781</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34385,28 +34595,28 @@
         <v>0.0557</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8437224697397904</v>
+        <v>-0.8073820417154766</v>
       </c>
       <c r="J7" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K7" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1556363630453357</v>
+        <v>0.1430302618844453</v>
       </c>
       <c r="M7" t="n">
-        <v>11.30119970413506</v>
+        <v>11.42072535885667</v>
       </c>
       <c r="N7" t="n">
-        <v>219.7980361718857</v>
+        <v>223.8982086636859</v>
       </c>
       <c r="O7" t="n">
-        <v>14.8255872117055</v>
+        <v>14.96322855080701</v>
       </c>
       <c r="P7" t="n">
-        <v>332.8505681689468</v>
+        <v>332.4656774518398</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34463,28 +34673,28 @@
         <v>0.056</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.327872371362874</v>
+        <v>-1.27729819606808</v>
       </c>
       <c r="J8" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K8" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2459226053112592</v>
+        <v>0.2281031187314269</v>
       </c>
       <c r="M8" t="n">
-        <v>13.67120122226583</v>
+        <v>13.82867515198559</v>
       </c>
       <c r="N8" t="n">
-        <v>312.0803486128235</v>
+        <v>320.9761668370886</v>
       </c>
       <c r="O8" t="n">
-        <v>17.66579600846855</v>
+        <v>17.91580773610525</v>
       </c>
       <c r="P8" t="n">
-        <v>334.5242453210121</v>
+        <v>333.9941052058239</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34541,28 +34751,28 @@
         <v>0.0566</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.226156166836202</v>
+        <v>-1.179949988588861</v>
       </c>
       <c r="J9" t="n">
+        <v>471</v>
+      </c>
+      <c r="K9" t="n">
         <v>468</v>
       </c>
-      <c r="K9" t="n">
-        <v>465</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.2589337676978566</v>
+        <v>0.2402964522348596</v>
       </c>
       <c r="M9" t="n">
-        <v>12.19694445328458</v>
+        <v>12.36644489339849</v>
       </c>
       <c r="N9" t="n">
-        <v>249.7412932798501</v>
+        <v>257.3037622143171</v>
       </c>
       <c r="O9" t="n">
-        <v>15.80320515844334</v>
+        <v>16.04069082721555</v>
       </c>
       <c r="P9" t="n">
-        <v>330.7950266148394</v>
+        <v>330.3115479231124</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34619,28 +34829,28 @@
         <v>0.0488</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.110053764585911</v>
+        <v>-1.07012577676746</v>
       </c>
       <c r="J10" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K10" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1924463958397288</v>
+        <v>0.1799684229714896</v>
       </c>
       <c r="M10" t="n">
-        <v>13.68400365252123</v>
+        <v>13.78523085522604</v>
       </c>
       <c r="N10" t="n">
-        <v>297.7916224876739</v>
+        <v>302.6752312467337</v>
       </c>
       <c r="O10" t="n">
-        <v>17.25663995358522</v>
+        <v>17.39756394575786</v>
       </c>
       <c r="P10" t="n">
-        <v>329.4494483776281</v>
+        <v>329.0296410753754</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34697,28 +34907,28 @@
         <v>0.0619</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.240113574510566</v>
+        <v>-1.205519592816326</v>
       </c>
       <c r="J11" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K11" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L11" t="n">
-        <v>0.223846914630726</v>
+        <v>0.2136419791270661</v>
       </c>
       <c r="M11" t="n">
-        <v>13.42827757933266</v>
+        <v>13.5265987610797</v>
       </c>
       <c r="N11" t="n">
-        <v>308.8223962230987</v>
+        <v>311.9956203134787</v>
       </c>
       <c r="O11" t="n">
-        <v>17.57334334220722</v>
+        <v>17.663397756759</v>
       </c>
       <c r="P11" t="n">
-        <v>325.6340099078658</v>
+        <v>325.2710569885636</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34775,28 +34985,28 @@
         <v>0.0561</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.876057443023896</v>
+        <v>-0.8519746607351116</v>
       </c>
       <c r="J12" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K12" t="n">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="L12" t="n">
-        <v>0.110460245840815</v>
+        <v>0.1056221156012566</v>
       </c>
       <c r="M12" t="n">
-        <v>14.92228250683766</v>
+        <v>14.94708347473052</v>
       </c>
       <c r="N12" t="n">
-        <v>354.8892631462097</v>
+        <v>355.422387905521</v>
       </c>
       <c r="O12" t="n">
-        <v>18.83850480123647</v>
+        <v>18.85264936038224</v>
       </c>
       <c r="P12" t="n">
-        <v>314.4042520460629</v>
+        <v>314.1493916586199</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34853,28 +35063,28 @@
         <v>0.0425</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7742533363435173</v>
+        <v>-0.7450944045899648</v>
       </c>
       <c r="J13" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K13" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09805310834043302</v>
+        <v>0.091638432399202</v>
       </c>
       <c r="M13" t="n">
-        <v>14.32076614513651</v>
+        <v>14.40118760784886</v>
       </c>
       <c r="N13" t="n">
-        <v>319.2774447223882</v>
+        <v>320.8950370054493</v>
       </c>
       <c r="O13" t="n">
-        <v>17.86833637254426</v>
+        <v>17.91354339614163</v>
       </c>
       <c r="P13" t="n">
-        <v>317.3801903665376</v>
+        <v>317.0742065225967</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34931,28 +35141,28 @@
         <v>0.0451</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.133154380695106</v>
+        <v>-1.093676373258798</v>
       </c>
       <c r="J14" t="n">
+        <v>471</v>
+      </c>
+      <c r="K14" t="n">
         <v>468</v>
       </c>
-      <c r="K14" t="n">
-        <v>465</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1584747733916254</v>
+        <v>0.1488239051561017</v>
       </c>
       <c r="M14" t="n">
-        <v>15.7869750678436</v>
+        <v>15.90197158067333</v>
       </c>
       <c r="N14" t="n">
-        <v>394.5279016911032</v>
+        <v>398.6626112527861</v>
       </c>
       <c r="O14" t="n">
-        <v>19.86272644153122</v>
+        <v>19.96653728749144</v>
       </c>
       <c r="P14" t="n">
-        <v>321.0786379225895</v>
+        <v>320.6645015802626</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35009,28 +35219,28 @@
         <v>0.0413</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9940024539631798</v>
+        <v>-0.966310932047918</v>
       </c>
       <c r="J15" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K15" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L15" t="n">
-        <v>0.178694911116173</v>
+        <v>0.1706953132121561</v>
       </c>
       <c r="M15" t="n">
-        <v>12.80727442269871</v>
+        <v>12.88256971680523</v>
       </c>
       <c r="N15" t="n">
-        <v>262.3060107424039</v>
+        <v>263.9180862444907</v>
       </c>
       <c r="O15" t="n">
-        <v>16.19586400110855</v>
+        <v>16.24555589213526</v>
       </c>
       <c r="P15" t="n">
-        <v>314.6466574967795</v>
+        <v>314.3560557942264</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -35091,28 +35301,28 @@
         <v>0.0337</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5990198476711425</v>
+        <v>-0.5751829531545092</v>
       </c>
       <c r="J16" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K16" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08491300977384575</v>
+        <v>0.0790007452380449</v>
       </c>
       <c r="M16" t="n">
-        <v>11.83630327651375</v>
+        <v>11.89663754798201</v>
       </c>
       <c r="N16" t="n">
-        <v>223.6978677515252</v>
+        <v>224.7033946343152</v>
       </c>
       <c r="O16" t="n">
-        <v>14.9565326112547</v>
+        <v>14.99010989400395</v>
       </c>
       <c r="P16" t="n">
-        <v>305.3719026336535</v>
+        <v>305.1216020680668</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -35173,28 +35383,28 @@
         <v>0.1173</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1876308900110672</v>
+        <v>-0.1795158422863162</v>
       </c>
       <c r="J17" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K17" t="n">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01407848416980517</v>
+        <v>0.01305193617827416</v>
       </c>
       <c r="M17" t="n">
-        <v>7.877470805316316</v>
+        <v>7.862585478465309</v>
       </c>
       <c r="N17" t="n">
-        <v>140.3003915967062</v>
+        <v>139.6742302792959</v>
       </c>
       <c r="O17" t="n">
-        <v>11.84484662613688</v>
+        <v>11.81838526530997</v>
       </c>
       <c r="P17" t="n">
-        <v>309.0748558667139</v>
+        <v>308.9887611191006</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -35236,7 +35446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R469"/>
+  <dimension ref="A1:R472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78151,6 +78361,282 @@
         </is>
       </c>
     </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>-45.90691318177737,170.55155732186392</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>-45.907274914669564,170.55057973645197</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>-45.90727207159105,170.54967951164403</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>-45.90721812367111,170.54878466715056</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>-45.90721918693864,170.5478862577403</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>-45.90721930603216,170.54698919289717</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>-45.907240847159756,170.54609097099228</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>-45.90721547456364,170.54519351900444</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>-45.90715281975408,170.5442987062718</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>-45.90706419422752,170.54339928512718</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>-45.90705150994986,170.5425052418002</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>-45.907071014409325,170.54161077266474</t>
+        </is>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>-45.90707079565729,170.5407060352332</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>-45.90699629300903,170.53979515746298</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>-45.907020296963026,170.53887938448398</t>
+        </is>
+      </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>-45.90712151695287,170.53798411008475</t>
+        </is>
+      </c>
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>-45.90685301715533,170.55156912663662</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>-45.90724610271799,170.55058404778313</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>-45.90727494319774,170.54967921871992</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>-45.90722997423977,170.5487835683218</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>-45.90722916821096,170.54788581286314</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>-45.907214178059625,170.54698921560905</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>-45.907234369723035,170.54609099975252</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>-45.907201450915345,170.54519430976893</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>-45.9071377199337,170.54429964658732</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>-45.907021550974925,170.54339920481937</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>-45.90695723398807,170.5425068947581</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>-45.907030912864286,170.54161270600085</t>
+        </is>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>-45.9070589203308,170.54070605531982</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>-45.906989641091,170.53979477115234</t>
+        </is>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>-45.907023253731445,170.5388797674718</t>
+        </is>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>-45.90712232020093,170.5379842560005</t>
+        </is>
+      </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>-45.90685301715533,170.55156912663662</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>-45.90724610271799,170.55058404778313</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>-45.907261213328205,170.54968061926309</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>-45.907217944117036,170.54878468379948</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>-45.907218827253146,170.5478862737719</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>-45.90720131314605,170.5469892725878</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>-45.90721493741289,170.54609108603296</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>-45.90718239313679,170.54519538439675</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>-45.90711102560825,170.5443013089291</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>-45.907021550974925,170.54339920481937</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>-45.906885267603954,170.54250815654981</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>-45.907030912864286,170.54161270600085</t>
+        </is>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>-45.9070589203308,170.54070605531982</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>-45.90695808942561,170.53979293878794</t>
+        </is>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>-45.906995119631944,170.5388761232858</t>
+        </is>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>-45.90711723296324,170.53798333186745</t>
+        </is>
+      </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
